--- a/東広島市_西条エリア7蔵_主要日本酒一覧.xlsx
+++ b/東広島市_西条エリア7蔵_主要日本酒一覧.xlsx
@@ -8,12 +8,16 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="概要" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主要銘柄" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="選定基準" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ブランド一覧" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ブランド・中核銘柄" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主要銘柄" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="選定基準" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要銘柄'!$A$4:$J$39</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'選定基準'!$A$4:$B$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ブランド一覧'!$A$4:$H$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ブランド・中核銘柄'!$A$4:$R$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'主要銘柄'!$A$4:$M$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'選定基準'!$A$4:$B$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -205,26 +209,73 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T_400410" displayName="T_400410" ref="A4:J39" headerRowCount="1">
-  <autoFilter ref="A4:J39"/>
-  <tableColumns count="10">
-    <tableColumn id="1" name="酒蔵"/>
-    <tableColumn id="2" name="商品名"/>
-    <tableColumn id="3" name="分類"/>
-    <tableColumn id="4" name="甘辛目安"/>
-    <tableColumn id="5" name="日本酒度"/>
-    <tableColumn id="6" name="おすすめの飲み方"/>
-    <tableColumn id="7" name="容量"/>
-    <tableColumn id="8" name="流通区分"/>
-    <tableColumn id="9" name="選定理由"/>
-    <tableColumn id="10" name="出典URL"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T_593330" displayName="T_593330" ref="A4:H16" headerRowCount="1">
+  <autoFilter ref="A4:H16"/>
+  <tableColumns count="8">
+    <tableColumn id="1" name="エリア"/>
+    <tableColumn id="2" name="酒蔵"/>
+    <tableColumn id="3" name="ブランド"/>
+    <tableColumn id="4" name="区分"/>
+    <tableColumn id="5" name="公式URL"/>
+    <tableColumn id="6" name="A中核銘柄数"/>
+    <tableColumn id="7" name="B主要銘柄数"/>
+    <tableColumn id="8" name="確認日"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T_510675" displayName="T_510675" ref="A4:B9" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T_934440" displayName="T_934440" ref="A4:R50" headerRowCount="1">
+  <autoFilter ref="A4:R50"/>
+  <tableColumns count="18">
+    <tableColumn id="1" name="エリア"/>
+    <tableColumn id="2" name="酒蔵"/>
+    <tableColumn id="3" name="ブランド"/>
+    <tableColumn id="4" name="シリーズ"/>
+    <tableColumn id="5" name="中核銘柄"/>
+    <tableColumn id="6" name="優先度"/>
+    <tableColumn id="7" name="位置づけ"/>
+    <tableColumn id="8" name="ブランド収録判定"/>
+    <tableColumn id="9" name="個別SKU確認"/>
+    <tableColumn id="10" name="分類"/>
+    <tableColumn id="11" name="甘辛目安"/>
+    <tableColumn id="12" name="日本酒度"/>
+    <tableColumn id="13" name="おすすめの飲み方"/>
+    <tableColumn id="14" name="主要容量"/>
+    <tableColumn id="15" name="流通区分"/>
+    <tableColumn id="16" name="確認日"/>
+    <tableColumn id="17" name="根拠URL"/>
+    <tableColumn id="18" name="商品出典URL"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="T_671225" displayName="T_671225" ref="A4:M39" headerRowCount="1">
+  <autoFilter ref="A4:M39"/>
+  <tableColumns count="13">
+    <tableColumn id="1" name="酒蔵"/>
+    <tableColumn id="2" name="ブランド"/>
+    <tableColumn id="3" name="シリーズ"/>
+    <tableColumn id="4" name="商品名"/>
+    <tableColumn id="5" name="分類"/>
+    <tableColumn id="6" name="甘辛目安"/>
+    <tableColumn id="7" name="日本酒度"/>
+    <tableColumn id="8" name="おすすめの飲み方"/>
+    <tableColumn id="9" name="容量"/>
+    <tableColumn id="10" name="流通区分"/>
+    <tableColumn id="11" name="SKU確認"/>
+    <tableColumn id="12" name="選定理由"/>
+    <tableColumn id="13" name="出典URL"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="T_930275" displayName="T_930275" ref="A4:B9" headerRowCount="1">
   <autoFilter ref="A4:B9"/>
   <tableColumns count="2">
     <tableColumn id="1" name="基準"/>
@@ -702,1706 +753,6727 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="38" customWidth="1" min="9" max="9"/>
-    <col width="42" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>東広島市 西条エリア7蔵 主要日本酒一覧</t>
+          <t>東広島市 西条エリア7蔵 ブランド一覧</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>各酒蔵 最大5商品。人気順位ではなく、現行流通・酒質の幅・公開情報の充実度を基準に選定。</t>
+          <t>主ブランド・別ブランド・主要シリーズを整理。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
+          <t>エリア</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
           <t>酒蔵</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>商品名</t>
-        </is>
-      </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>分類</t>
+          <t>ブランド</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>甘辛目安</t>
+          <t>区分</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>日本酒度</t>
+          <t>公式URL</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>おすすめの飲み方</t>
+          <t>A中核銘柄数</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>容量</t>
+          <t>B主要銘柄数</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>流通区分</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>選定理由</t>
-        </is>
-      </c>
-      <c r="J4" s="6" t="inlineStr">
-        <is>
-          <t>出典URL</t>
+          <t>確認日</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
+          <t>西条エリア7蔵</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
           <t>賀茂鶴酒造</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>純米大吟醸 大吟峰</t>
-        </is>
-      </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>純米大吟醸</t>
+          <t>賀茂鶴</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr"/>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>冷酒 / 燗酒</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>720ml / 1,800ml</t>
-        </is>
+          <t>主ブランド</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>https://www.kamotsuru.jp/</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="G5" s="7" t="n">
+        <v>2</v>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>一般流通</t>
-        </is>
-      </c>
-      <c r="I5" s="7" t="inlineStr">
-        <is>
-          <t>現行流通・純米大吟醸枠／定番性と酒質の幅を考慮</t>
-        </is>
-      </c>
-      <c r="J5" s="8" t="inlineStr">
-        <is>
-          <t>https://shop.kamotsuru.jp/SHOP/originalbottle_DK-B1.html</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
+          <t>西条エリア7蔵</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
           <t>賀茂鶴酒造</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>大吟醸 特製ゴールド賀茂鶴</t>
-        </is>
-      </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>大吟醸</t>
+          <t>酒中在心</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="E6" s="9" t="inlineStr"/>
-      <c r="F6" s="9" t="inlineStr">
-        <is>
-          <t>冷酒 / 燗酒</t>
-        </is>
-      </c>
-      <c r="G6" s="9" t="inlineStr">
-        <is>
-          <t>180ml / 300ml / 720ml / 1,800ml</t>
-        </is>
+          <t>販路限定主要シリーズ</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>https://shop.kamotsuru.jp/SHOP/346441/346696/list.html</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
-          <t>一般流通</t>
-        </is>
-      </c>
-      <c r="I6" s="9" t="inlineStr">
-        <is>
-          <t>現行流通・大吟醸枠／定番性と酒質の幅を考慮</t>
-        </is>
-      </c>
-      <c r="J6" s="8" t="inlineStr">
-        <is>
-          <t>https://shop.kamotsuru.jp/SHOP/GK-A2.html</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>賀茂鶴酒造</t>
+          <t>西条エリア7蔵</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>吟醸辛口</t>
+          <t>白牡丹酒造</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>吟醸</t>
+          <t>白牡丹</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>辛口</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="inlineStr"/>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>冷酒 / 燗酒</t>
-        </is>
-      </c>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>300ml / 1,800ml</t>
-        </is>
+          <t>主ブランド</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>https://www.hakubotan.co.jp/products/</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G7" s="7" t="n">
+        <v>2</v>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>一般流通</t>
-        </is>
-      </c>
-      <c r="I7" s="7" t="inlineStr">
-        <is>
-          <t>現行流通・吟醸枠／定番性と酒質の幅を考慮</t>
-        </is>
-      </c>
-      <c r="J7" s="8" t="inlineStr">
-        <is>
-          <t>https://shop.kamotsuru.jp/SHOP/LG-A1.html</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>賀茂鶴酒造</t>
+          <t>西条エリア7蔵</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>純米酒</t>
+          <t>白牡丹酒造</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>純米</t>
+          <t>藝陽男山</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="E8" s="9" t="inlineStr"/>
-      <c r="F8" s="9" t="inlineStr">
-        <is>
-          <t>冷酒 / 冷やして / 燗酒</t>
-        </is>
-      </c>
-      <c r="G8" s="9" t="inlineStr">
-        <is>
-          <t>180ml / 300ml / 1,800ml</t>
-        </is>
+          <t>別ブランド・生酛系</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>https://www.hakubotan.co.jp/products/</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="H8" s="9" t="inlineStr">
         <is>
-          <t>一般流通</t>
-        </is>
-      </c>
-      <c r="I8" s="9" t="inlineStr">
-        <is>
-          <t>現行流通・純米枠／定番性と酒質の幅を考慮</t>
-        </is>
-      </c>
-      <c r="J8" s="8" t="inlineStr">
-        <is>
-          <t>https://shop.kamotsuru.jp/SHOP/junmai1800.html</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>賀茂鶴酒造</t>
+          <t>西条エリア7蔵</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>特別本醸造 超特撰特等酒</t>
+          <t>西條鶴醸造</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>特別本醸造</t>
+          <t>西條鶴</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr"/>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>冷酒 / ぬる燗 / 燗酒</t>
-        </is>
-      </c>
-      <c r="G9" s="7" t="inlineStr">
-        <is>
-          <t>1,800ml</t>
-        </is>
+          <t>主ブランド</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>https://saijotsuru.co.jp/</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G9" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>一般流通</t>
-        </is>
-      </c>
-      <c r="I9" s="7" t="inlineStr">
-        <is>
-          <t>現行流通・特別本醸造枠／定番性と酒質の幅を考慮</t>
-        </is>
-      </c>
-      <c r="J9" s="8" t="inlineStr">
-        <is>
-          <t>https://shop.kamotsuru.jp/SHOP/tokutou1800.html</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>白牡丹酒造</t>
+          <t>西条エリア7蔵</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>山田錦 純米大吟醸 氷華</t>
+          <t>亀齢酒造</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>純米大吟醸</t>
+          <t>亀齢</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>やや甘口</t>
+          <t>主ブランド</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>-1.5</t>
-        </is>
-      </c>
-      <c r="F10" s="9" t="inlineStr">
-        <is>
-          <t>常温 / 冷酒</t>
-        </is>
-      </c>
-      <c r="G10" s="9" t="inlineStr"/>
+          <t>https://kireikireikirei.jimdofree.com/</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="G10" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>一般流通</t>
-        </is>
-      </c>
-      <c r="I10" s="9" t="inlineStr">
-        <is>
-          <t>現行流通・純米大吟醸枠／定番性と酒質の幅を考慮</t>
-        </is>
-      </c>
-      <c r="J10" s="8" t="inlineStr">
-        <is>
-          <t>https://www.hakubotan.co.jp/products/%e3%80%90%e5%87%8d%e7%b5%90%e7%94%9f%e9%85%92%e3%80%91%e3%80%90%e6%97%a5%e6%9c%ac%e9%85%92-%e7%99%bd%e7%89%a1%e4%b8%b9%e3%80%91%e5%b1%b1%e7%94%b0%e9%8c%a6-%e7%b4%94%e7%b1%b3%e5%a4%a7%e5%90%9f%e9%86%b8/</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>白牡丹酒造</t>
+          <t>西条エリア7蔵</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>大吟醸</t>
+          <t>亀齢酒造</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>大吟醸</t>
+          <t>亀齢萬年</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>やや辛口</t>
+          <t>主要シリーズブランド</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>+3</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>常温</t>
-        </is>
-      </c>
-      <c r="G11" s="7" t="inlineStr"/>
+          <t>https://kireikireikirei.jimdofree.com/</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>一般流通</t>
-        </is>
-      </c>
-      <c r="I11" s="7" t="inlineStr">
-        <is>
-          <t>現行流通・大吟醸枠／定番性と酒質の幅を考慮</t>
-        </is>
-      </c>
-      <c r="J11" s="8" t="inlineStr">
-        <is>
-          <t>https://www.hakubotan.co.jp/products/%e3%80%90%e6%97%a5%e6%9c%ac%e9%85%92-%e7%99%bd%e7%89%a1%e4%b8%b9%e3%80%91%e5%a4%a7%e5%90%9f%e9%86%b8-1-8l%e7%93%b6%e8%a9%b0/</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>白牡丹酒造</t>
+          <t>西条エリア7蔵</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>広島八反 純米吟醸</t>
+          <t>福美人酒造</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>純米吟醸</t>
+          <t>福美人</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>やや辛口</t>
+          <t>主ブランド</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>+1.5</t>
-        </is>
-      </c>
-      <c r="F12" s="9" t="inlineStr">
-        <is>
-          <t>常温</t>
-        </is>
-      </c>
-      <c r="G12" s="9" t="inlineStr">
-        <is>
-          <t>720ml / 1,800ml</t>
-        </is>
+          <t>https://www.fukubijin.co.jp/product.html</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="G12" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>一般流通</t>
-        </is>
-      </c>
-      <c r="I12" s="9" t="inlineStr">
-        <is>
-          <t>現行流通・純米吟醸枠／定番性と酒質の幅を考慮</t>
-        </is>
-      </c>
-      <c r="J12" s="8" t="inlineStr">
-        <is>
-          <t>https://www.hakubotan.co.jp/products/%e3%80%90%e6%97%a5%e6%9c%ac%e9%85%92-%e7%99%bd%e7%89%a1%e4%b8%b9%e3%80%91%e5%ba%83%e5%b3%b6%e5%85%ab%e5%8f%8d-%e7%b4%94%e7%b1%b3%e5%90%9f%e9%86%b8-1-8l%e7%93%b6%e8%a9%b0/</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>白牡丹酒造</t>
+          <t>西条エリア7蔵</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>純米酒</t>
+          <t>賀茂泉酒造</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>純米</t>
+          <t>賀茂泉</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>中口</t>
+          <t>主ブランド</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>+0.5</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>常温 / ぬる燗 / 熱燗 / 燗酒</t>
-        </is>
-      </c>
-      <c r="G13" s="7" t="inlineStr"/>
+          <t>https://www.kamoizumi.co.jp/sake/index.php</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G13" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>一般流通</t>
-        </is>
-      </c>
-      <c r="I13" s="7" t="inlineStr">
-        <is>
-          <t>現行流通・純米枠／定番性と酒質の幅を考慮</t>
-        </is>
-      </c>
-      <c r="J13" s="8" t="inlineStr">
-        <is>
-          <t>https://www.hakubotan.co.jp/products/%e3%80%90%e6%97%a5%e6%9c%ac%e9%85%92-%e7%99%bd%e7%89%a1%e4%b8%b9%e3%80%91%e7%b4%94%e7%b1%b3%e9%85%92-1-8l%e7%93%b6%e8%a9%b0/</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>白牡丹酒造</t>
+          <t>西条エリア7蔵</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>本醸造 生貯蔵酒</t>
+          <t>賀茂泉酒造</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>本醸造</t>
+          <t>ROCK HOPPER</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>中口</t>
+          <t>現行生原酒シリーズ</t>
         </is>
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>+0.5</t>
-        </is>
-      </c>
-      <c r="F14" s="9" t="inlineStr">
-        <is>
-          <t>常温</t>
-        </is>
-      </c>
-      <c r="G14" s="9" t="inlineStr">
-        <is>
-          <t>180ml / 300ml</t>
-        </is>
+          <t>https://www.kamoizumi.co.jp/sake/index.php</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>一般流通</t>
-        </is>
-      </c>
-      <c r="I14" s="9" t="inlineStr">
-        <is>
-          <t>現行流通・本醸造枠／定番性と酒質の幅を考慮</t>
-        </is>
-      </c>
-      <c r="J14" s="8" t="inlineStr">
-        <is>
-          <t>https://www.hakubotan.co.jp/products/%e3%80%90%e6%97%a5%e6%9c%ac%e9%85%92-%e7%99%bd%e7%89%a1%e4%b8%b9%e3%80%91%e6%9c%ac%e9%86%b8%e9%80%a0-%e7%94%9f%e8%b2%af%e8%94%b5%e9%85%92-300ml%e7%93%b6%e8%a9%b0/</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>西條鶴醸造</t>
+          <t>西条エリア7蔵</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>純米大吟醸原酒「神髄」</t>
+          <t>賀茂泉酒造</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>純米大吟醸</t>
+          <t>COKUN</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="inlineStr"/>
-      <c r="F15" s="7" t="inlineStr">
-        <is>
-          <t>常温</t>
-        </is>
-      </c>
-      <c r="G15" s="7" t="inlineStr">
-        <is>
-          <t>180ml / 500ml / 720ml / 1,800ml</t>
-        </is>
+          <t>低アルコール系ブランド</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>https://www.kamoizumi.co.jp/sake/index.php</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>一般流通</t>
-        </is>
-      </c>
-      <c r="I15" s="7" t="inlineStr">
-        <is>
-          <t>現行流通・純米大吟醸枠／定番性と酒質の幅を考慮</t>
-        </is>
-      </c>
-      <c r="J15" s="8" t="inlineStr">
-        <is>
-          <t>https://saijotsuru.co.jp/?pid=180817561</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>西條鶴醸造</t>
+          <t>西条エリア7蔵</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>純米吟醸「大地の冠」</t>
+          <t>山陽鶴酒造</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
+          <t>山陽鶴</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>主ブランド</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>https://sanyotsuru.jp/</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="G16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:H16"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:R50"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="28" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="42" customWidth="1" min="17" max="17"/>
+    <col width="42" customWidth="1" min="18" max="18"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>東広島市 西条エリア7蔵 ブランド・中核銘柄</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>A＝絶対に落とさない代表・蔵元推奨等、B＝主要定番・高級・注目ライン。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>エリア</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>酒蔵</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>ブランド</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>シリーズ</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>中核銘柄</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>優先度</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>位置づけ</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>ブランド収録判定</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>個別SKU確認</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>分類</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>甘辛目安</t>
+        </is>
+      </c>
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>日本酒度</t>
+        </is>
+      </c>
+      <c r="M4" s="6" t="inlineStr">
+        <is>
+          <t>おすすめの飲み方</t>
+        </is>
+      </c>
+      <c r="N4" s="6" t="inlineStr">
+        <is>
+          <t>主要容量</t>
+        </is>
+      </c>
+      <c r="O4" s="6" t="inlineStr">
+        <is>
+          <t>流通区分</t>
+        </is>
+      </c>
+      <c r="P4" s="6" t="inlineStr">
+        <is>
+          <t>確認日</t>
+        </is>
+      </c>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
+          <t>根拠URL</t>
+        </is>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>商品出典URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>西条エリア7蔵</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>賀茂鶴酒造</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>賀茂鶴</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr"/>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>大吟醸 特製ゴールド賀茂鶴</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>公式直近1年販売本数ベース晩酌1位・賀茂鶴を代表する銘柄</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>大吟醸</t>
+        </is>
+      </c>
+      <c r="K5" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="L5" s="7" t="inlineStr"/>
+      <c r="M5" s="7" t="inlineStr">
+        <is>
+          <t>冷酒 / 燗酒</t>
+        </is>
+      </c>
+      <c r="N5" s="7" t="inlineStr">
+        <is>
+          <t>180ml / 300ml / 720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="O5" s="7" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="P5" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q5" s="7" t="inlineStr">
+        <is>
+          <t>https://shop.kamotsuru.jp/SHOP/346441/346696/list.html</t>
+        </is>
+      </c>
+      <c r="R5" s="7" t="inlineStr">
+        <is>
+          <t>https://shop.kamotsuru.jp/SHOP/GK-A2.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>西条エリア7蔵</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>賀茂鶴酒造</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>賀茂鶴</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr"/>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>純米吟醸 一滴入魂</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>公式晩酌おすすめ2位・アジア圏で人気</t>
+        </is>
+      </c>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J6" s="9" t="inlineStr">
+        <is>
           <t>純米吟醸</t>
         </is>
       </c>
+      <c r="K6" s="9" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="L6" s="9" t="inlineStr"/>
+      <c r="M6" s="9" t="inlineStr">
+        <is>
+          <t>冷酒 / ぬる燗 / 燗酒</t>
+        </is>
+      </c>
+      <c r="N6" s="9" t="inlineStr">
+        <is>
+          <t>300ml / 720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="O6" s="9" t="inlineStr">
+        <is>
+          <t>限定流通</t>
+        </is>
+      </c>
+      <c r="P6" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q6" s="9" t="inlineStr">
+        <is>
+          <t>https://shop.kamotsuru.jp/SHOP/346441/346696/list.html</t>
+        </is>
+      </c>
+      <c r="R6" s="9" t="inlineStr">
+        <is>
+          <t>https://shop.kamotsuru.jp/SHOP/GP-A1.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>西条エリア7蔵</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>賀茂鶴酒造</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>酒中在心</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr"/>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>酒中在心 橙 純米吟醸 生もと 八反35号</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>公式晩酌おすすめ3位・販路限定の主要シリーズ</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>純米吟醸</t>
+        </is>
+      </c>
+      <c r="K7" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="L7" s="7" t="inlineStr"/>
+      <c r="M7" s="7" t="inlineStr">
+        <is>
+          <t>冷酒 / 常温 / ぬる燗 / 燗酒</t>
+        </is>
+      </c>
+      <c r="N7" s="7" t="inlineStr">
+        <is>
+          <t>720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="O7" s="7" t="inlineStr">
+        <is>
+          <t>限定流通</t>
+        </is>
+      </c>
+      <c r="P7" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q7" s="7" t="inlineStr">
+        <is>
+          <t>https://shop.kamotsuru.jp/SHOP/346441/346696/list.html</t>
+        </is>
+      </c>
+      <c r="R7" s="7" t="inlineStr">
+        <is>
+          <t>https://shop.kamotsuru.jp/SHOP/shutyuzaishin-daidai_1800.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>西条エリア7蔵</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>賀茂鶴酒造</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>賀茂鶴</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr"/>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>本醸造 からくち</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>公式晩酌おすすめ4位・料飲店人気の食中酒</t>
+        </is>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="inlineStr">
+        <is>
+          <t>本醸造</t>
+        </is>
+      </c>
+      <c r="K8" s="9" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="L8" s="9" t="inlineStr"/>
+      <c r="M8" s="9" t="inlineStr">
+        <is>
+          <t>冷酒 / 燗酒</t>
+        </is>
+      </c>
+      <c r="N8" s="9" t="inlineStr">
+        <is>
+          <t>180ml / 300ml / 720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="O8" s="9" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="P8" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q8" s="9" t="inlineStr">
+        <is>
+          <t>https://shop.kamotsuru.jp/SHOP/346441/346696/list.html</t>
+        </is>
+      </c>
+      <c r="R8" s="9" t="inlineStr">
+        <is>
+          <t>https://shop.kamotsuru.jp/SHOP/honkara1800.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>西条エリア7蔵</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>賀茂鶴酒造</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>賀茂鶴</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr"/>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>特別本醸造 超特撰特等酒</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>公式晩酌おすすめ5位・長年の定番</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>特別本醸造</t>
+        </is>
+      </c>
+      <c r="K9" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="L9" s="7" t="inlineStr"/>
+      <c r="M9" s="7" t="inlineStr">
+        <is>
+          <t>冷酒 / ぬる燗 / 燗酒</t>
+        </is>
+      </c>
+      <c r="N9" s="7" t="inlineStr">
+        <is>
+          <t>300ml / 720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="O9" s="7" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="P9" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q9" s="7" t="inlineStr">
+        <is>
+          <t>https://shop.kamotsuru.jp/SHOP/346441/346696/list.html</t>
+        </is>
+      </c>
+      <c r="R9" s="7" t="inlineStr">
+        <is>
+          <t>https://shop.kamotsuru.jp/SHOP/tokutou1800.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>西条エリア7蔵</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>賀茂鶴酒造</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>賀茂鶴</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr"/>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>大吟醸 賀茂鶴 双鶴</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>代表高級酒・公式ブランドカテゴリ</t>
+        </is>
+      </c>
+      <c r="H10" s="9" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J10" s="9" t="inlineStr">
+        <is>
+          <t>大吟醸</t>
+        </is>
+      </c>
+      <c r="K10" s="9" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="L10" s="9" t="inlineStr"/>
+      <c r="M10" s="9" t="inlineStr">
+        <is>
+          <t>冷酒 / 燗酒</t>
+        </is>
+      </c>
+      <c r="N10" s="9" t="inlineStr">
+        <is>
+          <t>180ml / 720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="O10" s="9" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="P10" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q10" s="9" t="inlineStr">
+        <is>
+          <t>https://shop.kamotsuru.jp/SHOP/346441/346696/list.html</t>
+        </is>
+      </c>
+      <c r="R10" s="9" t="inlineStr">
+        <is>
+          <t>https://shop.kamotsuru.jp/SHOP/SK-A1.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>西条エリア7蔵</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>賀茂鶴酒造</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>賀茂鶴</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr"/>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>純米大吟醸 大吟峰</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>公式ブランドカテゴリの主要純米大吟醸</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>純米大吟醸</t>
+        </is>
+      </c>
+      <c r="K11" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="L11" s="7" t="inlineStr"/>
+      <c r="M11" s="7" t="inlineStr">
+        <is>
+          <t>冷酒 / 燗酒</t>
+        </is>
+      </c>
+      <c r="N11" s="7" t="inlineStr">
+        <is>
+          <t>720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="O11" s="7" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="P11" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q11" s="7" t="inlineStr">
+        <is>
+          <t>https://shop.kamotsuru.jp/SHOP/346441/346696/list.html</t>
+        </is>
+      </c>
+      <c r="R11" s="7" t="inlineStr">
+        <is>
+          <t>https://shop.kamotsuru.jp/SHOP/originalbottle_DK-B1.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>西条エリア7蔵</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>白牡丹酒造</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>白牡丹</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr"/>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>大吟醸</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>公式現行定番・300/720/1800ml展開</t>
+        </is>
+      </c>
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J12" s="9" t="inlineStr">
+        <is>
+          <t>大吟醸</t>
+        </is>
+      </c>
+      <c r="K12" s="9" t="inlineStr">
+        <is>
+          <t>やや辛口</t>
+        </is>
+      </c>
+      <c r="L12" s="9" t="inlineStr">
+        <is>
+          <t>+3</t>
+        </is>
+      </c>
+      <c r="M12" s="9" t="inlineStr">
+        <is>
+          <t>常温 / 冷酒</t>
+        </is>
+      </c>
+      <c r="N12" s="9" t="inlineStr">
+        <is>
+          <t>300ml / 720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="O12" s="9" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="P12" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q12" s="9" t="inlineStr">
+        <is>
+          <t>https://www.hakubotan.co.jp/products/</t>
+        </is>
+      </c>
+      <c r="R12" s="9" t="inlineStr">
+        <is>
+          <t>https://www.hakubotan.co.jp/products/</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>西条エリア7蔵</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>白牡丹酒造</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>白牡丹</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr"/>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>純米吟醸</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>公式現行定番・ワイングラスアワード受賞</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>純米吟醸</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="inlineStr">
+        <is>
+          <t>中口</t>
+        </is>
+      </c>
+      <c r="L13" s="7" t="inlineStr">
+        <is>
+          <t>+0.5</t>
+        </is>
+      </c>
+      <c r="M13" s="7" t="inlineStr">
+        <is>
+          <t>常温</t>
+        </is>
+      </c>
+      <c r="N13" s="7" t="inlineStr">
+        <is>
+          <t>720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="O13" s="7" t="inlineStr">
+        <is>
+          <t>限定流通</t>
+        </is>
+      </c>
+      <c r="P13" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q13" s="7" t="inlineStr">
+        <is>
+          <t>https://www.hakubotan.co.jp/products/</t>
+        </is>
+      </c>
+      <c r="R13" s="7" t="inlineStr">
+        <is>
+          <t>https://www.hakubotan.co.jp/products/%e3%80%90%e6%97%a5%e6%9c%ac%e9%85%92-%e7%99%bd%e7%89%a1%e4%b8%b9%e3%80%91%e7%b4%94%e7%b1%b3%e5%90%9f%e9%86%b8-1-8l%e7%93%b6%e8%a9%b0/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>西条エリア7蔵</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>白牡丹酒造</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>白牡丹</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr"/>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>純米酒</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>公式定番・燗酒コンテスト受賞</t>
+        </is>
+      </c>
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J14" s="9" t="inlineStr">
+        <is>
+          <t>純米</t>
+        </is>
+      </c>
+      <c r="K14" s="9" t="inlineStr">
+        <is>
+          <t>中口</t>
+        </is>
+      </c>
+      <c r="L14" s="9" t="inlineStr">
+        <is>
+          <t>+0.5</t>
+        </is>
+      </c>
+      <c r="M14" s="9" t="inlineStr">
+        <is>
+          <t>常温 / ぬる燗 / 熱燗 / 燗酒</t>
+        </is>
+      </c>
+      <c r="N14" s="9" t="inlineStr">
+        <is>
+          <t>300ml / 720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="O14" s="9" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="P14" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q14" s="9" t="inlineStr">
+        <is>
+          <t>https://www.hakubotan.co.jp/products/</t>
+        </is>
+      </c>
+      <c r="R14" s="9" t="inlineStr">
+        <is>
+          <t>https://www.hakubotan.co.jp/products/%e3%80%90%e6%97%a5%e6%9c%ac%e9%85%92-%e7%99%bd%e7%89%a1%e4%b8%b9%e3%80%91%e7%b4%94%e7%b1%b3%e9%85%92-1-8l%e7%93%b6%e8%a9%b0/</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>西条エリア7蔵</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>白牡丹酒造</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>白牡丹</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>万年蔵</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>純米大吟醸 原酒 万年蔵 杜氏 鹿島正</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>公式高級ライン・広島らしさを前面に出す商品</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>純米大吟醸</t>
+        </is>
+      </c>
+      <c r="K15" s="7" t="inlineStr">
+        <is>
+          <t>甘口</t>
+        </is>
+      </c>
+      <c r="L15" s="7" t="inlineStr">
+        <is>
+          <t>-8</t>
+        </is>
+      </c>
+      <c r="M15" s="7" t="inlineStr">
+        <is>
+          <t>常温 / ぬる燗 / 燗酒</t>
+        </is>
+      </c>
+      <c r="N15" s="7" t="inlineStr">
+        <is>
+          <t>720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="O15" s="7" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="P15" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q15" s="7" t="inlineStr">
+        <is>
+          <t>https://www.hakubotan.co.jp/products/</t>
+        </is>
+      </c>
+      <c r="R15" s="7" t="inlineStr">
+        <is>
+          <t>https://www.hakubotan.co.jp/products/%e3%80%90%e6%97%a5%e6%9c%ac%e9%85%92-%e7%99%bd%e7%89%a1%e4%b8%b9%e3%80%91%e7%b4%94%e7%b1%b3%e5%a4%a7%e5%90%9f%e9%86%b8-%e5%8e%9f%e9%85%92-%e4%b8%87%e5%b9%b4%e8%94%b5-%e6%9d%9c%e6%b0%8f-%e9%b9%bf/</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>西条エリア7蔵</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>白牡丹酒造</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>白牡丹</t>
+        </is>
+      </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="E16" s="9" t="inlineStr"/>
+          <t>Paeon</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>Paeon(ピオン)</t>
+        </is>
+      </c>
       <c r="F16" s="9" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>720ml / 1,800ml</t>
+          <t>ワイングラスでおいしい日本酒アワード2026最高金賞</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J16" s="9" t="inlineStr">
+        <is>
+          <t>特別純米</t>
+        </is>
+      </c>
+      <c r="K16" s="9" t="inlineStr">
+        <is>
+          <t>やや甘口</t>
+        </is>
+      </c>
+      <c r="L16" s="9" t="inlineStr">
+        <is>
+          <t>-1.5</t>
+        </is>
+      </c>
+      <c r="M16" s="9" t="inlineStr">
+        <is>
+          <t>常温 / 冷酒</t>
+        </is>
+      </c>
+      <c r="N16" s="9" t="inlineStr">
+        <is>
+          <t>500ml</t>
+        </is>
+      </c>
+      <c r="O16" s="9" t="inlineStr">
+        <is>
           <t>一般流通</t>
         </is>
       </c>
-      <c r="I16" s="9" t="inlineStr">
-        <is>
-          <t>現行流通・純米吟醸枠／定番性と酒質の幅を考慮</t>
-        </is>
-      </c>
-      <c r="J16" s="8" t="inlineStr">
-        <is>
-          <t>https://saijotsuru.co.jp/?pid=157617368</t>
+      <c r="P16" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q16" s="9" t="inlineStr">
+        <is>
+          <t>https://www.hakubotan.co.jp/%E3%83%AF%E3%82%A4%E3%83%B3%E3%82%B0%E3%83%A9%E3%82%B9%E3%81%A7%E3%81%8A%E3%81%84%E3%81%97%E3%81%84%E6%97%A5%E6%9C%AC%E9%85%92%E3%82%A2%E3%83%AF%E3%83%BC%E3%83%892026/</t>
+        </is>
+      </c>
+      <c r="R16" s="9" t="inlineStr">
+        <is>
+          <t>https://www.hakubotan.co.jp/products/%E3%80%90%E6%97%A5%E6%9C%AC%E9%85%92-%E7%99%BD%E7%89%A1%E4%B8%B9%E3%80%91paeon%E3%83%94%E3%82%AA%E3%83%B3%E3%80%90%E6%96%B0%E3%80%91/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>西條鶴醸造</t>
+          <t>西条エリア7蔵</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>吟醸酒「ゴールド西條鶴」</t>
+          <t>白牡丹酒造</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>吟醸</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="E17" s="7" t="inlineStr"/>
+          <t>白牡丹</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr"/>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>純米大吟醸 悠星(ゆうせい)</t>
+        </is>
+      </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>冷酒 / 常温 / ぬる燗</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>720ml</t>
+          <t>2026ワイングラスアワード金賞・現行おすすめ</t>
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>個別SKU未確認</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>純米大吟醸</t>
+        </is>
+      </c>
+      <c r="K17" s="7" t="inlineStr">
+        <is>
+          <t>中口</t>
+        </is>
+      </c>
+      <c r="L17" s="7" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="M17" s="7" t="inlineStr">
+        <is>
+          <t>常温</t>
+        </is>
+      </c>
+      <c r="N17" s="7" t="inlineStr"/>
+      <c r="O17" s="7" t="inlineStr">
+        <is>
           <t>一般流通</t>
         </is>
       </c>
-      <c r="I17" s="7" t="inlineStr">
-        <is>
-          <t>現行流通・吟醸枠／定番性と酒質の幅を考慮</t>
-        </is>
-      </c>
-      <c r="J17" s="8" t="inlineStr">
-        <is>
-          <t>https://saijotsuru.co.jp/?pid=157617449</t>
+      <c r="P17" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q17" s="7" t="inlineStr">
+        <is>
+          <t>https://www.hakubotan.co.jp/products/</t>
+        </is>
+      </c>
+      <c r="R17" s="7" t="inlineStr">
+        <is>
+          <t>https://www.hakubotan.co.jp/products/%e3%80%90%e6%97%a5%e6%9c%ac%e9%85%92-%e7%99%bd%e7%89%a1%e4%b8%b9%e3%80%91%e7%b4%94%e7%b1%b3%e5%a4%a7%e5%90%9f%e9%86%b8-%e6%82%a0%e6%98%9f%e3%82%86%e3%81%86%e3%81%9b%e3%81%84720ml%e7%93%b6%e8%a9%b0/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>西條鶴醸造</t>
+          <t>西条エリア7蔵</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>純米酒「大地の風」</t>
+          <t>白牡丹酒造</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>純米</t>
-        </is>
-      </c>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="E18" s="9" t="inlineStr"/>
+          <t>白牡丹</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr"/>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>広島八反 純米吟醸</t>
+        </is>
+      </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>冷酒 / 常温 / 熱燗</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
+          <t>広島酒米を前面に出す現行主要商品</t>
+        </is>
+      </c>
+      <c r="H18" s="9" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J18" s="9" t="inlineStr">
+        <is>
+          <t>純米吟醸</t>
+        </is>
+      </c>
+      <c r="K18" s="9" t="inlineStr">
+        <is>
+          <t>やや辛口</t>
+        </is>
+      </c>
+      <c r="L18" s="9" t="inlineStr">
+        <is>
+          <t>+1.5</t>
+        </is>
+      </c>
+      <c r="M18" s="9" t="inlineStr">
+        <is>
+          <t>常温</t>
+        </is>
+      </c>
+      <c r="N18" s="9" t="inlineStr">
+        <is>
           <t>720ml / 1,800ml</t>
         </is>
       </c>
-      <c r="H18" s="9" t="inlineStr">
+      <c r="O18" s="9" t="inlineStr">
         <is>
           <t>一般流通</t>
         </is>
       </c>
-      <c r="I18" s="9" t="inlineStr">
-        <is>
-          <t>現行流通・純米枠／定番性と酒質の幅を考慮</t>
-        </is>
-      </c>
-      <c r="J18" s="8" t="inlineStr">
-        <is>
-          <t>https://saijotsuru.co.jp/?pid=157617524</t>
+      <c r="P18" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q18" s="9" t="inlineStr">
+        <is>
+          <t>https://www.hakubotan.co.jp/products/</t>
+        </is>
+      </c>
+      <c r="R18" s="9" t="inlineStr">
+        <is>
+          <t>https://www.hakubotan.co.jp/products/%e3%80%90%e6%97%a5%e6%9c%ac%e9%85%92-%e7%99%bd%e7%89%a1%e4%b8%b9%e3%80%91%e5%ba%83%e5%b3%b6%e5%85%ab%e5%8f%8d-%e7%b4%94%e7%b1%b3%e5%90%9f%e9%86%b8-1-8l%e7%93%b6%e8%a9%b0/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
+          <t>西条エリア7蔵</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
           <t>西條鶴醸造</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>純米大吟醸「西鶴」</t>
-        </is>
-      </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
+          <t>西條鶴</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr"/>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>純米大吟醸原酒「神髄」</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>公式おすすめ・純米大吟醸の中心商品</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
           <t>純米大吟醸</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="K19" s="7" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr"/>
-      <c r="F19" s="7" t="inlineStr">
+      <c r="L19" s="7" t="inlineStr"/>
+      <c r="M19" s="7" t="inlineStr">
         <is>
           <t>常温</t>
         </is>
       </c>
-      <c r="G19" s="7" t="inlineStr">
-        <is>
-          <t>720ml</t>
-        </is>
-      </c>
-      <c r="H19" s="7" t="inlineStr">
+      <c r="N19" s="7" t="inlineStr">
+        <is>
+          <t>180ml / 500ml / 720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="O19" s="7" t="inlineStr">
         <is>
           <t>一般流通</t>
         </is>
       </c>
-      <c r="I19" s="7" t="inlineStr">
-        <is>
-          <t>現行流通・純米大吟醸枠／定番性と酒質の幅を考慮</t>
-        </is>
-      </c>
-      <c r="J19" s="8" t="inlineStr">
-        <is>
-          <t>https://saijotsuru.co.jp/?pid=157617273</t>
+      <c r="P19" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q19" s="7" t="inlineStr">
+        <is>
+          <t>https://saijotsuru.co.jp/?gid=2464785&amp;mode=grp</t>
+        </is>
+      </c>
+      <c r="R19" s="7" t="inlineStr">
+        <is>
+          <t>https://saijotsuru.co.jp/?pid=180817561</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>亀齢酒造</t>
+          <t>西条エリア7蔵</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>純米大吟醸 亀香</t>
+          <t>西條鶴醸造</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>純米大吟醸</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="E20" s="9" t="inlineStr"/>
+          <t>西條鶴</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr"/>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>辛口純米酒『きんさいや』</t>
+        </is>
+      </c>
       <c r="F20" s="9" t="inlineStr">
         <is>
-          <t>常温 / 冷酒</t>
-        </is>
-      </c>
-      <c r="G20" s="9" t="inlineStr"/>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>公式おすすめ商品</t>
+        </is>
+      </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J20" s="9" t="inlineStr">
+        <is>
+          <t>純米</t>
+        </is>
+      </c>
+      <c r="K20" s="9" t="inlineStr">
+        <is>
+          <t>辛口</t>
+        </is>
+      </c>
+      <c r="L20" s="9" t="inlineStr"/>
+      <c r="M20" s="9" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N20" s="9" t="inlineStr">
+        <is>
+          <t>500ml</t>
+        </is>
+      </c>
+      <c r="O20" s="9" t="inlineStr">
+        <is>
           <t>一般流通</t>
         </is>
       </c>
-      <c r="I20" s="9" t="inlineStr">
-        <is>
-          <t>現行流通・純米大吟醸枠／定番性と酒質の幅を考慮</t>
-        </is>
-      </c>
-      <c r="J20" s="8" t="inlineStr">
-        <is>
-          <t>https://kireikireikirei.jimdofree.com/酒蔵土産売場-まねきや/</t>
+      <c r="P20" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q20" s="9" t="inlineStr">
+        <is>
+          <t>https://saijotsuru.co.jp/?gid=2464785&amp;mode=grp</t>
+        </is>
+      </c>
+      <c r="R20" s="9" t="inlineStr">
+        <is>
+          <t>https://saijotsuru.co.jp/?pid=189850838</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>亀齢酒造</t>
+          <t>西条エリア7蔵</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>亀齢 大吟醸 創</t>
+          <t>西條鶴醸造</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>大吟醸</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>辛口</t>
-        </is>
-      </c>
+          <t>西條鶴</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr"/>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>＋５</t>
+          <t>純米酒「大地の風」</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>燗酒</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>720ml</t>
+          <t>公式おすすめ・定番純米</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J21" s="7" t="inlineStr">
+        <is>
+          <t>純米</t>
+        </is>
+      </c>
+      <c r="K21" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="L21" s="7" t="inlineStr"/>
+      <c r="M21" s="7" t="inlineStr">
+        <is>
+          <t>冷酒 / 常温 / 熱燗</t>
+        </is>
+      </c>
+      <c r="N21" s="7" t="inlineStr">
+        <is>
+          <t>720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="O21" s="7" t="inlineStr">
+        <is>
           <t>一般流通</t>
         </is>
       </c>
-      <c r="I21" s="7" t="inlineStr">
-        <is>
-          <t>現行流通・大吟醸枠／定番性と酒質の幅を考慮</t>
-        </is>
-      </c>
-      <c r="J21" s="8" t="inlineStr">
-        <is>
-          <t>https://www.hiroshimasake.com/product/17</t>
+      <c r="P21" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q21" s="7" t="inlineStr">
+        <is>
+          <t>https://saijotsuru.co.jp/?gid=2464785&amp;mode=grp&amp;sort=n</t>
+        </is>
+      </c>
+      <c r="R21" s="7" t="inlineStr">
+        <is>
+          <t>https://saijotsuru.co.jp/?pid=157617524</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>亀齢酒造</t>
+          <t>西条エリア7蔵</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>亀齢 純米吟醸 六拾</t>
+          <t>西條鶴醸造</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
+          <t>西條鶴</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr"/>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>純米吟醸「大地の冠」</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G22" s="9" t="inlineStr">
+        <is>
+          <t>公式おすすめ・定番純米吟醸</t>
+        </is>
+      </c>
+      <c r="H22" s="9" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I22" s="9" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J22" s="9" t="inlineStr">
+        <is>
           <t>純米吟醸</t>
         </is>
       </c>
-      <c r="D22" s="9" t="inlineStr">
+      <c r="K22" s="9" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
       </c>
-      <c r="E22" s="9" t="inlineStr"/>
-      <c r="F22" s="9" t="inlineStr">
+      <c r="L22" s="9" t="inlineStr"/>
+      <c r="M22" s="9" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="G22" s="9" t="inlineStr">
-        <is>
-          <t>720ml</t>
-        </is>
-      </c>
-      <c r="H22" s="9" t="inlineStr">
+      <c r="N22" s="9" t="inlineStr">
+        <is>
+          <t>720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="O22" s="9" t="inlineStr">
         <is>
           <t>一般流通</t>
         </is>
       </c>
-      <c r="I22" s="9" t="inlineStr">
-        <is>
-          <t>現行流通・純米吟醸枠／定番性と酒質の幅を考慮</t>
-        </is>
-      </c>
-      <c r="J22" s="8" t="inlineStr">
-        <is>
-          <t>https://e-sake.jp/article/article-1369/</t>
+      <c r="P22" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q22" s="9" t="inlineStr">
+        <is>
+          <t>https://saijotsuru.co.jp/?gid=2464785&amp;mode=grp&amp;sort=n</t>
+        </is>
+      </c>
+      <c r="R22" s="9" t="inlineStr">
+        <is>
+          <t>https://saijotsuru.co.jp/?pid=157617368</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>亀齢酒造</t>
+          <t>西条エリア7蔵</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>亀齢 辛口純米 八拾</t>
+          <t>西條鶴醸造</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>純米</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>辛口</t>
-        </is>
-      </c>
+          <t>西條鶴</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr"/>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>＋５</t>
+          <t>吟醸酒「ゴールド西條鶴」</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>燗酒</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>720ml / 1,800ml</t>
+          <t>公式贈答・おすすめ定番</t>
         </is>
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J23" s="7" t="inlineStr">
+        <is>
+          <t>吟醸</t>
+        </is>
+      </c>
+      <c r="K23" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="L23" s="7" t="inlineStr"/>
+      <c r="M23" s="7" t="inlineStr">
+        <is>
+          <t>冷酒 / 常温 / ぬる燗</t>
+        </is>
+      </c>
+      <c r="N23" s="7" t="inlineStr">
+        <is>
+          <t>720ml</t>
+        </is>
+      </c>
+      <c r="O23" s="7" t="inlineStr">
+        <is>
           <t>一般流通</t>
         </is>
       </c>
-      <c r="I23" s="7" t="inlineStr">
-        <is>
-          <t>現行流通・純米枠／定番性と酒質の幅を考慮</t>
-        </is>
-      </c>
-      <c r="J23" s="8" t="inlineStr">
-        <is>
-          <t>https://www.hiroshimasake.com/product/37</t>
+      <c r="P23" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q23" s="7" t="inlineStr">
+        <is>
+          <t>https://saijotsuru.co.jp/?gid=2539031&amp;mode=grp&amp;sort=p</t>
+        </is>
+      </c>
+      <c r="R23" s="7" t="inlineStr">
+        <is>
+          <t>https://saijotsuru.co.jp/?pid=157617449</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>亀齢酒造</t>
+          <t>西条エリア7蔵</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>亀齢 上撰</t>
+          <t>西條鶴醸造</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>本醸造</t>
-        </is>
-      </c>
-      <c r="D24" s="9" t="inlineStr">
-        <is>
-          <t>辛口</t>
-        </is>
-      </c>
-      <c r="E24" s="9" t="inlineStr"/>
+          <t>西條鶴</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr"/>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>純米大吟醸「西鶴」</t>
+        </is>
+      </c>
       <c r="F24" s="9" t="inlineStr">
         <is>
-          <t>冷酒 / 燗酒</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>1,800ml</t>
+          <t>公式純米大吟醸カテゴリの現行商品</t>
         </is>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I24" s="9" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J24" s="9" t="inlineStr">
+        <is>
+          <t>純米大吟醸</t>
+        </is>
+      </c>
+      <c r="K24" s="9" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="L24" s="9" t="inlineStr"/>
+      <c r="M24" s="9" t="inlineStr">
+        <is>
+          <t>常温</t>
+        </is>
+      </c>
+      <c r="N24" s="9" t="inlineStr">
+        <is>
+          <t>720ml</t>
+        </is>
+      </c>
+      <c r="O24" s="9" t="inlineStr">
+        <is>
           <t>一般流通</t>
         </is>
       </c>
-      <c r="I24" s="9" t="inlineStr">
-        <is>
-          <t>現行流通・本醸造枠／定番性と酒質の幅を考慮</t>
-        </is>
-      </c>
-      <c r="J24" s="8" t="inlineStr">
-        <is>
-          <t>https://osake-style.com/SHOP/11012948.html</t>
+      <c r="P24" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q24" s="9" t="inlineStr">
+        <is>
+          <t>https://saijotsuru.co.jp/?cbid=2659464&amp;csid=0&amp;mode=cate</t>
+        </is>
+      </c>
+      <c r="R24" s="9" t="inlineStr">
+        <is>
+          <t>https://saijotsuru.co.jp/?pid=157617273</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>福美人酒造</t>
+          <t>西条エリア7蔵</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>大吟醸 蔵乃華 （ くらのはな ）</t>
+          <t>亀齢酒造</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>大吟醸</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>やや辛口</t>
-        </is>
-      </c>
+          <t>亀齢</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr"/>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>+2.0</t>
+          <t>亀齢 辛口純米 八拾</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>常温 / 冷酒</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
+          <t>現行流通で代表銘柄として広く扱われる辛口純米</t>
+        </is>
+      </c>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J25" s="7" t="inlineStr">
+        <is>
+          <t>純米</t>
+        </is>
+      </c>
+      <c r="K25" s="7" t="inlineStr">
+        <is>
+          <t>辛口</t>
+        </is>
+      </c>
+      <c r="L25" s="7" t="inlineStr">
+        <is>
+          <t>＋５</t>
+        </is>
+      </c>
+      <c r="M25" s="7" t="inlineStr">
+        <is>
+          <t>燗酒</t>
+        </is>
+      </c>
+      <c r="N25" s="7" t="inlineStr">
+        <is>
           <t>720ml / 1,800ml</t>
         </is>
       </c>
-      <c r="H25" s="7" t="inlineStr">
+      <c r="O25" s="7" t="inlineStr">
         <is>
           <t>一般流通</t>
         </is>
       </c>
-      <c r="I25" s="7" t="inlineStr">
-        <is>
-          <t>現行流通・大吟醸枠／定番性と酒質の幅を考慮</t>
-        </is>
-      </c>
-      <c r="J25" s="8" t="inlineStr">
-        <is>
-          <t>https://www.fukubijin.co.jp/SHOP/1020.html</t>
+      <c r="P25" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q25" s="7" t="inlineStr">
+        <is>
+          <t>https://www.yamatoya-e.com/SHOP/kire005c.html</t>
+        </is>
+      </c>
+      <c r="R25" s="7" t="inlineStr">
+        <is>
+          <t>https://www.hiroshimasake.com/product/37</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>福美人酒造</t>
+          <t>西条エリア7蔵</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>純米吟醸</t>
+          <t>亀齢酒造</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>純米吟醸</t>
-        </is>
-      </c>
-      <c r="D26" s="9" t="inlineStr">
+          <t>亀齢</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr"/>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>亀齢 大吟醸 創</t>
+        </is>
+      </c>
+      <c r="F26" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G26" s="9" t="inlineStr">
+        <is>
+          <t>現行流通の代表高級酒</t>
+        </is>
+      </c>
+      <c r="H26" s="9" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I26" s="9" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J26" s="9" t="inlineStr">
+        <is>
+          <t>大吟醸</t>
+        </is>
+      </c>
+      <c r="K26" s="9" t="inlineStr">
         <is>
           <t>辛口</t>
         </is>
       </c>
-      <c r="E26" s="9" t="inlineStr">
-        <is>
-          <t>+4.0</t>
-        </is>
-      </c>
-      <c r="F26" s="9" t="inlineStr">
+      <c r="L26" s="9" t="inlineStr">
+        <is>
+          <t>＋５</t>
+        </is>
+      </c>
+      <c r="M26" s="9" t="inlineStr">
         <is>
           <t>燗酒</t>
         </is>
       </c>
-      <c r="G26" s="9" t="inlineStr">
-        <is>
-          <t>720ml / 1,800ml</t>
-        </is>
-      </c>
-      <c r="H26" s="9" t="inlineStr">
+      <c r="N26" s="9" t="inlineStr">
+        <is>
+          <t>720ml</t>
+        </is>
+      </c>
+      <c r="O26" s="9" t="inlineStr">
         <is>
           <t>一般流通</t>
         </is>
       </c>
-      <c r="I26" s="9" t="inlineStr">
-        <is>
-          <t>現行流通・純米吟醸枠／定番性と酒質の幅を考慮</t>
-        </is>
-      </c>
-      <c r="J26" s="8" t="inlineStr">
-        <is>
-          <t>https://www.fukubijin.co.jp/SHOP/1221.html</t>
+      <c r="P26" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q26" s="9" t="inlineStr">
+        <is>
+          <t>https://kireikireikirei.jimdofree.com/</t>
+        </is>
+      </c>
+      <c r="R26" s="9" t="inlineStr">
+        <is>
+          <t>https://www.hiroshimasake.com/product/17</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>福美人酒造</t>
+          <t>西条エリア7蔵</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>特別純米酒「ひめあま」</t>
+          <t>亀齢酒造</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>特別純米</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>甘口</t>
-        </is>
-      </c>
+          <t>亀齢萬年</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr"/>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>-16.0</t>
+          <t>亀齢萬年 純米大吟醸原酒五拾 生酒</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>冷酒</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>300ml / 720ml</t>
+          <t>亀齢萬年を代表する2026年現行の純米大吟醸ライン</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>一般流通</t>
+          <t>収録済</t>
         </is>
       </c>
       <c r="I27" s="7" t="inlineStr">
         <is>
-          <t>現行流通・特別純米枠／定番性と酒質の幅を考慮</t>
-        </is>
-      </c>
-      <c r="J27" s="8" t="inlineStr">
-        <is>
-          <t>https://www.fukubijin.co.jp/SHOP/2080.html</t>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J27" s="7" t="inlineStr">
+        <is>
+          <t>純米大吟醸</t>
+        </is>
+      </c>
+      <c r="K27" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="L27" s="7" t="inlineStr"/>
+      <c r="M27" s="7" t="inlineStr">
+        <is>
+          <t>燗酒</t>
+        </is>
+      </c>
+      <c r="N27" s="7" t="inlineStr">
+        <is>
+          <t>720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="O27" s="7" t="inlineStr">
+        <is>
+          <t>季節商品</t>
+        </is>
+      </c>
+      <c r="P27" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q27" s="7" t="inlineStr">
+        <is>
+          <t>https://www.hiroshimasake.com/product-list/6</t>
+        </is>
+      </c>
+      <c r="R27" s="7" t="inlineStr">
+        <is>
+          <t>https://www.hiroshimasake.com/product/552</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>福美人酒造</t>
+          <t>西条エリア7蔵</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>純米酒</t>
+          <t>亀齢酒造</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>純米</t>
-        </is>
-      </c>
-      <c r="D28" s="9" t="inlineStr">
-        <is>
-          <t>やや辛口</t>
-        </is>
-      </c>
+          <t>亀齢</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr"/>
       <c r="E28" s="9" t="inlineStr">
         <is>
-          <t>+3.0</t>
+          <t>亀齢 純米吟醸 六拾</t>
         </is>
       </c>
       <c r="F28" s="9" t="inlineStr">
         <is>
-          <t>燗酒</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G28" s="9" t="inlineStr">
         <is>
+          <t>2026年東広島10蔵定期便採用の現行純米吟醸</t>
+        </is>
+      </c>
+      <c r="H28" s="9" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I28" s="9" t="inlineStr">
+        <is>
+          <t>個別SKU未確認</t>
+        </is>
+      </c>
+      <c r="J28" s="9" t="inlineStr">
+        <is>
+          <t>純米吟醸</t>
+        </is>
+      </c>
+      <c r="K28" s="9" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="L28" s="9" t="inlineStr"/>
+      <c r="M28" s="9" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N28" s="9" t="inlineStr">
+        <is>
           <t>720ml</t>
         </is>
       </c>
-      <c r="H28" s="9" t="inlineStr">
+      <c r="O28" s="9" t="inlineStr">
         <is>
           <t>一般流通</t>
         </is>
       </c>
-      <c r="I28" s="9" t="inlineStr">
-        <is>
-          <t>現行流通・純米枠／定番性と酒質の幅を考慮</t>
-        </is>
-      </c>
-      <c r="J28" s="8" t="inlineStr">
-        <is>
-          <t>https://www.fukubijin.co.jp/SHOP/2020.html</t>
+      <c r="P28" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q28" s="9" t="inlineStr">
+        <is>
+          <t>https://e-sake.jp/article/article-1369/</t>
+        </is>
+      </c>
+      <c r="R28" s="9" t="inlineStr">
+        <is>
+          <t>https://e-sake.jp/article/article-1369/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>福美人酒造</t>
+          <t>西条エリア7蔵</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>本醸造 舞</t>
+          <t>亀齢酒造</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>本醸造</t>
-        </is>
-      </c>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="E29" s="7" t="inlineStr"/>
+          <t>亀齢</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr"/>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>亀齢 上撰</t>
+        </is>
+      </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>燗酒</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
+          <t>地元で継続流通する定番酒</t>
+        </is>
+      </c>
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J29" s="7" t="inlineStr">
+        <is>
+          <t>普通酒・上撰</t>
+        </is>
+      </c>
+      <c r="K29" s="7" t="inlineStr">
+        <is>
+          <t>辛口</t>
+        </is>
+      </c>
+      <c r="L29" s="7" t="inlineStr"/>
+      <c r="M29" s="7" t="inlineStr">
+        <is>
+          <t>冷酒 / 燗酒</t>
+        </is>
+      </c>
+      <c r="N29" s="7" t="inlineStr">
+        <is>
           <t>1,800ml</t>
         </is>
       </c>
-      <c r="H29" s="7" t="inlineStr">
+      <c r="O29" s="7" t="inlineStr">
         <is>
           <t>一般流通</t>
         </is>
       </c>
-      <c r="I29" s="7" t="inlineStr">
-        <is>
-          <t>現行流通・本醸造枠／定番性と酒質の幅を考慮</t>
-        </is>
-      </c>
-      <c r="J29" s="8" t="inlineStr">
-        <is>
-          <t>https://www.fukubijin.co.jp/SHOP/3010.html</t>
+      <c r="P29" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q29" s="7" t="inlineStr">
+        <is>
+          <t>https://osake-style.com/SHOP/11012948.html</t>
+        </is>
+      </c>
+      <c r="R29" s="7" t="inlineStr">
+        <is>
+          <t>https://osake-style.com/SHOP/11012948.html</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>賀茂泉酒造</t>
+          <t>西条エリア7蔵</t>
         </is>
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>純米大吟醸｢広大｣</t>
+          <t>亀齢酒造</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>純米大吟醸</t>
-        </is>
-      </c>
-      <c r="D30" s="9" t="inlineStr">
-        <is>
-          <t>やや辛口</t>
-        </is>
-      </c>
+          <t>亀齢</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr"/>
       <c r="E30" s="9" t="inlineStr">
         <is>
-          <t>+3.0</t>
+          <t>亀齢 無濾過 五段仕込純米酒 八九(はちく) 生酒</t>
         </is>
       </c>
       <c r="F30" s="9" t="inlineStr">
         <is>
-          <t>冷酒 / 燗酒</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
-          <t>720ml</t>
+          <t>2026年現行流通の個性派純米</t>
         </is>
       </c>
       <c r="H30" s="9" t="inlineStr">
         <is>
-          <t>一般流通</t>
+          <t>収録済</t>
         </is>
       </c>
       <c r="I30" s="9" t="inlineStr">
         <is>
-          <t>現行流通・純米大吟醸枠／定番性と酒質の幅を考慮</t>
-        </is>
-      </c>
-      <c r="J30" s="8" t="inlineStr">
-        <is>
-          <t>https://online.kamoizumi.com/?pid=188371751</t>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J30" s="9" t="inlineStr">
+        <is>
+          <t>純米</t>
+        </is>
+      </c>
+      <c r="K30" s="9" t="inlineStr">
+        <is>
+          <t>甘口</t>
+        </is>
+      </c>
+      <c r="L30" s="9" t="inlineStr">
+        <is>
+          <t>-18</t>
+        </is>
+      </c>
+      <c r="M30" s="9" t="inlineStr">
+        <is>
+          <t>燗酒</t>
+        </is>
+      </c>
+      <c r="N30" s="9" t="inlineStr">
+        <is>
+          <t>720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="O30" s="9" t="inlineStr">
+        <is>
+          <t>季節商品</t>
+        </is>
+      </c>
+      <c r="P30" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q30" s="9" t="inlineStr">
+        <is>
+          <t>https://www.sakeweb.jp/product-list/50</t>
+        </is>
+      </c>
+      <c r="R30" s="9" t="inlineStr">
+        <is>
+          <t>https://www.hiroshimasake.com/product/182</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>賀茂泉酒造</t>
+          <t>西条エリア7蔵</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>純米吟醸「古酒」</t>
+          <t>亀齢酒造</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
+          <t>亀齢</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>migaki</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>亀齢 純米吟醸 原形精米 migaki 無濾過生酒</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>2026年現行流通の原形精米シリーズ</t>
+        </is>
+      </c>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J31" s="7" t="inlineStr">
+        <is>
           <t>純米吟醸</t>
         </is>
       </c>
-      <c r="D31" s="7" t="inlineStr">
-        <is>
-          <t>やや辛口</t>
-        </is>
-      </c>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t>+1.5</t>
-        </is>
-      </c>
-      <c r="F31" s="7" t="inlineStr">
-        <is>
-          <t>冷酒 / 常温 / ぬる燗 / 燗酒</t>
-        </is>
-      </c>
-      <c r="G31" s="7" t="inlineStr">
-        <is>
-          <t>720ml</t>
-        </is>
-      </c>
-      <c r="H31" s="7" t="inlineStr">
-        <is>
-          <t>一般流通</t>
-        </is>
-      </c>
-      <c r="I31" s="7" t="inlineStr">
-        <is>
-          <t>現行流通・純米吟醸枠／定番性と酒質の幅を考慮</t>
-        </is>
-      </c>
-      <c r="J31" s="8" t="inlineStr">
-        <is>
-          <t>https://online.kamoizumi.com/?pid=188373081</t>
+      <c r="K31" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="L31" s="7" t="inlineStr"/>
+      <c r="M31" s="7" t="inlineStr">
+        <is>
+          <t>燗酒</t>
+        </is>
+      </c>
+      <c r="N31" s="7" t="inlineStr">
+        <is>
+          <t>720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="O31" s="7" t="inlineStr">
+        <is>
+          <t>季節商品</t>
+        </is>
+      </c>
+      <c r="P31" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q31" s="7" t="inlineStr">
+        <is>
+          <t>https://www.sakeweb.jp/product-list/50</t>
+        </is>
+      </c>
+      <c r="R31" s="7" t="inlineStr">
+        <is>
+          <t>https://www.hiroshimasake.com/product/550</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>賀茂泉酒造</t>
+          <t>西条エリア7蔵</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>純米酒 一 (はじめ)</t>
+          <t>福美人酒造</t>
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>純米</t>
-        </is>
-      </c>
-      <c r="D32" s="9" t="inlineStr">
-        <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="E32" s="9" t="inlineStr"/>
+          <t>福美人</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr"/>
+      <c r="E32" s="9" t="inlineStr">
+        <is>
+          <t>大吟醸 蔵乃華 （ くらのはな ）</t>
+        </is>
+      </c>
       <c r="F32" s="9" t="inlineStr">
         <is>
-          <t>冷酒 / ぬる燗 / 燗酒</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
-          <t>300ml / 720ml / 1,800ml</t>
+          <t>公式が代表的商品として掲載する上位酒</t>
         </is>
       </c>
       <c r="H32" s="9" t="inlineStr">
         <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I32" s="9" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J32" s="9" t="inlineStr">
+        <is>
+          <t>大吟醸</t>
+        </is>
+      </c>
+      <c r="K32" s="9" t="inlineStr">
+        <is>
+          <t>やや辛口</t>
+        </is>
+      </c>
+      <c r="L32" s="9" t="inlineStr">
+        <is>
+          <t>+2.0</t>
+        </is>
+      </c>
+      <c r="M32" s="9" t="inlineStr">
+        <is>
+          <t>常温 / 冷酒</t>
+        </is>
+      </c>
+      <c r="N32" s="9" t="inlineStr">
+        <is>
+          <t>720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="O32" s="9" t="inlineStr">
+        <is>
           <t>一般流通</t>
         </is>
       </c>
-      <c r="I32" s="9" t="inlineStr">
-        <is>
-          <t>現行流通・純米枠／定番性と酒質の幅を考慮</t>
-        </is>
-      </c>
-      <c r="J32" s="8" t="inlineStr">
-        <is>
-          <t>https://online.kamoizumi.com/?pid=188377558</t>
+      <c r="P32" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q32" s="9" t="inlineStr">
+        <is>
+          <t>https://www.fukubijin.co.jp/product.html</t>
+        </is>
+      </c>
+      <c r="R32" s="9" t="inlineStr">
+        <is>
+          <t>https://www.fukubijin.co.jp/SHOP/1020.html</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>賀茂泉酒造</t>
+          <t>西条エリア7蔵</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>朱泉普通酒</t>
+          <t>福美人酒造</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>普通酒・上撰</t>
-        </is>
-      </c>
-      <c r="D33" s="7" t="inlineStr">
+          <t>福美人</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr"/>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>大吟醸 西條酒造学校</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>蔵の歴史を体現する代表商品</t>
+        </is>
+      </c>
+      <c r="H33" s="7" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I33" s="7" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J33" s="7" t="inlineStr">
+        <is>
+          <t>大吟醸</t>
+        </is>
+      </c>
+      <c r="K33" s="7" t="inlineStr">
         <is>
           <t>やや辛口</t>
         </is>
       </c>
-      <c r="E33" s="7" t="inlineStr">
-        <is>
-          <t>+1.5</t>
-        </is>
-      </c>
-      <c r="F33" s="7" t="inlineStr">
-        <is>
-          <t>冷酒 / ぬる燗 / 熱燗 / 燗酒</t>
-        </is>
-      </c>
-      <c r="G33" s="7" t="inlineStr">
-        <is>
-          <t>1,800ml</t>
-        </is>
-      </c>
-      <c r="H33" s="7" t="inlineStr">
+      <c r="L33" s="7" t="inlineStr">
+        <is>
+          <t>+3.0</t>
+        </is>
+      </c>
+      <c r="M33" s="7" t="inlineStr">
+        <is>
+          <t>冷酒 / 常温</t>
+        </is>
+      </c>
+      <c r="N33" s="7" t="inlineStr">
+        <is>
+          <t>720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="O33" s="7" t="inlineStr">
         <is>
           <t>一般流通</t>
         </is>
       </c>
-      <c r="I33" s="7" t="inlineStr">
-        <is>
-          <t>現行流通・普通酒・上撰枠／定番性と酒質の幅を考慮</t>
-        </is>
-      </c>
-      <c r="J33" s="8" t="inlineStr">
-        <is>
-          <t>https://online.kamoizumi.com/?pid=188378827</t>
+      <c r="P33" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q33" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fukubijin.co.jp/product.html</t>
+        </is>
+      </c>
+      <c r="R33" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fukubijin.co.jp/SHOP/1120.html</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>賀茂泉酒造</t>
+          <t>西条エリア7蔵</t>
         </is>
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>朱泉本仕込</t>
+          <t>福美人酒造</t>
         </is>
       </c>
       <c r="C34" s="9" t="inlineStr">
         <is>
-          <t>その他</t>
-        </is>
-      </c>
-      <c r="D34" s="9" t="inlineStr">
-        <is>
-          <t>中口</t>
-        </is>
-      </c>
+          <t>福美人</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr"/>
       <c r="E34" s="9" t="inlineStr">
         <is>
-          <t>+1.0</t>
+          <t>純米吟醸</t>
         </is>
       </c>
       <c r="F34" s="9" t="inlineStr">
         <is>
-          <t>常温 / ぬる燗 / ロック</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G34" s="9" t="inlineStr">
         <is>
-          <t>180ml / 720ml / 1,800ml</t>
+          <t>公式が代表的商品として掲載する定番</t>
         </is>
       </c>
       <c r="H34" s="9" t="inlineStr">
         <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J34" s="9" t="inlineStr">
+        <is>
+          <t>純米吟醸</t>
+        </is>
+      </c>
+      <c r="K34" s="9" t="inlineStr">
+        <is>
+          <t>辛口</t>
+        </is>
+      </c>
+      <c r="L34" s="9" t="inlineStr">
+        <is>
+          <t>+4.0</t>
+        </is>
+      </c>
+      <c r="M34" s="9" t="inlineStr">
+        <is>
+          <t>燗酒</t>
+        </is>
+      </c>
+      <c r="N34" s="9" t="inlineStr">
+        <is>
+          <t>720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="O34" s="9" t="inlineStr">
+        <is>
           <t>一般流通</t>
         </is>
       </c>
-      <c r="I34" s="9" t="inlineStr">
-        <is>
-          <t>現行流通・その他枠／定番性と酒質の幅を考慮</t>
-        </is>
-      </c>
-      <c r="J34" s="8" t="inlineStr">
-        <is>
-          <t>https://www.kamoizumi.co.jp/sake/index.php</t>
+      <c r="P34" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q34" s="9" t="inlineStr">
+        <is>
+          <t>https://www.fukubijin.co.jp/product.html</t>
+        </is>
+      </c>
+      <c r="R34" s="9" t="inlineStr">
+        <is>
+          <t>https://www.fukubijin.co.jp/SHOP/1221.html</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>山陽鶴酒造</t>
+          <t>西条エリア7蔵</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>純米大吟醸 KUBO</t>
+          <t>福美人酒造</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>純米大吟醸</t>
-        </is>
-      </c>
-      <c r="D35" s="7" t="inlineStr">
-        <is>
-          <t>辛口</t>
-        </is>
-      </c>
+          <t>福美人</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr"/>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>純米酒</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>冷酒</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
+          <t>現行定番純米</t>
+        </is>
+      </c>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J35" s="7" t="inlineStr">
+        <is>
+          <t>純米</t>
+        </is>
+      </c>
+      <c r="K35" s="7" t="inlineStr">
+        <is>
+          <t>やや辛口</t>
+        </is>
+      </c>
+      <c r="L35" s="7" t="inlineStr">
+        <is>
+          <t>+3.0</t>
+        </is>
+      </c>
+      <c r="M35" s="7" t="inlineStr">
+        <is>
+          <t>燗酒</t>
+        </is>
+      </c>
+      <c r="N35" s="7" t="inlineStr">
+        <is>
           <t>720ml</t>
         </is>
       </c>
-      <c r="H35" s="7" t="inlineStr">
+      <c r="O35" s="7" t="inlineStr">
         <is>
           <t>一般流通</t>
         </is>
       </c>
-      <c r="I35" s="7" t="inlineStr">
-        <is>
-          <t>現行流通・純米大吟醸枠／定番性と酒質の幅を考慮</t>
-        </is>
-      </c>
-      <c r="J35" s="8" t="inlineStr">
-        <is>
-          <t>https://www.furusato.aeon.co.jp/gift-in-return/aaa72316281ae6d75280fb28cb3cae46/</t>
+      <c r="P35" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q35" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fukubijin.co.jp/SHOP/g23587/list.html</t>
+        </is>
+      </c>
+      <c r="R35" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fukubijin.co.jp/SHOP/2020.html</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>山陽鶴酒造</t>
+          <t>西条エリア7蔵</t>
         </is>
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>大吟醸</t>
+          <t>福美人酒造</t>
         </is>
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
-          <t>大吟醸</t>
-        </is>
-      </c>
-      <c r="D36" s="9" t="inlineStr">
+          <t>福美人</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr"/>
+      <c r="E36" s="9" t="inlineStr">
+        <is>
+          <t>上撰</t>
+        </is>
+      </c>
+      <c r="F36" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G36" s="9" t="inlineStr">
+        <is>
+          <t>公式が代表的商品として掲載する定番酒</t>
+        </is>
+      </c>
+      <c r="H36" s="9" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I36" s="9" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J36" s="9" t="inlineStr">
+        <is>
+          <t>普通酒・上撰</t>
+        </is>
+      </c>
+      <c r="K36" s="9" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
       </c>
-      <c r="E36" s="9" t="inlineStr"/>
-      <c r="F36" s="9" t="inlineStr">
-        <is>
-          <t>冷酒</t>
-        </is>
-      </c>
-      <c r="G36" s="9" t="inlineStr"/>
-      <c r="H36" s="9" t="inlineStr">
-        <is>
-          <t>一般流通</t>
-        </is>
-      </c>
-      <c r="I36" s="9" t="inlineStr">
-        <is>
-          <t>現行流通・大吟醸枠／定番性と酒質の幅を考慮</t>
-        </is>
-      </c>
-      <c r="J36" s="8" t="inlineStr">
-        <is>
-          <t>https://sanyotsuru.jp/archives/product/gosyu</t>
+      <c r="L36" s="9" t="inlineStr"/>
+      <c r="M36" s="9" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N36" s="9" t="inlineStr">
+        <is>
+          <t>720ml</t>
+        </is>
+      </c>
+      <c r="O36" s="9" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="P36" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q36" s="9" t="inlineStr">
+        <is>
+          <t>https://www.fukubijin.co.jp/product.html</t>
+        </is>
+      </c>
+      <c r="R36" s="9" t="inlineStr">
+        <is>
+          <t>https://www.fukubijin.co.jp/SHOP/2230.html</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
         <is>
+          <t>西条エリア7蔵</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>福美人酒造</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>福美人</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr"/>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>本醸造 舞</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>現行本醸造ライン</t>
+        </is>
+      </c>
+      <c r="H37" s="7" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I37" s="7" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J37" s="7" t="inlineStr">
+        <is>
+          <t>本醸造</t>
+        </is>
+      </c>
+      <c r="K37" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="L37" s="7" t="inlineStr"/>
+      <c r="M37" s="7" t="inlineStr">
+        <is>
+          <t>燗酒</t>
+        </is>
+      </c>
+      <c r="N37" s="7" t="inlineStr">
+        <is>
+          <t>1,800ml</t>
+        </is>
+      </c>
+      <c r="O37" s="7" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="P37" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q37" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fukubijin.co.jp/</t>
+        </is>
+      </c>
+      <c r="R37" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fukubijin.co.jp/SHOP/3010.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>西条エリア7蔵</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>賀茂泉酒造</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>賀茂泉</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr"/>
+      <c r="E38" s="9" t="inlineStr">
+        <is>
+          <t>純米吟醸「朱泉本仕込」</t>
+        </is>
+      </c>
+      <c r="F38" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G38" s="9" t="inlineStr">
+        <is>
+          <t>公式が「賀茂泉を代表するお酒」と明記</t>
+        </is>
+      </c>
+      <c r="H38" s="9" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I38" s="9" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J38" s="9" t="inlineStr">
+        <is>
+          <t>純米吟醸</t>
+        </is>
+      </c>
+      <c r="K38" s="9" t="inlineStr">
+        <is>
+          <t>中口</t>
+        </is>
+      </c>
+      <c r="L38" s="9" t="inlineStr">
+        <is>
+          <t>+1.0</t>
+        </is>
+      </c>
+      <c r="M38" s="9" t="inlineStr">
+        <is>
+          <t>常温 / ぬる燗 / ロック</t>
+        </is>
+      </c>
+      <c r="N38" s="9" t="inlineStr">
+        <is>
+          <t>180ml / 720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="O38" s="9" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="P38" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q38" s="9" t="inlineStr">
+        <is>
+          <t>https://www.kamoizumi.co.jp/sake/index.php</t>
+        </is>
+      </c>
+      <c r="R38" s="9" t="inlineStr">
+        <is>
+          <t>https://www.kamoizumi.co.jp/sake/index.php</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>西条エリア7蔵</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>賀茂泉酒造</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>賀茂泉</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr"/>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>純米大吟醸「壽」</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>公式が醸造技術の極み・究極のお酒と説明</t>
+        </is>
+      </c>
+      <c r="H39" s="7" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J39" s="7" t="inlineStr">
+        <is>
+          <t>純米大吟醸</t>
+        </is>
+      </c>
+      <c r="K39" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="L39" s="7" t="inlineStr"/>
+      <c r="M39" s="7" t="inlineStr">
+        <is>
+          <t>冷酒 / 冷やして / 燗酒</t>
+        </is>
+      </c>
+      <c r="N39" s="7" t="inlineStr">
+        <is>
+          <t>720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="O39" s="7" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="P39" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q39" s="7" t="inlineStr">
+        <is>
+          <t>https://www.kamoizumi.co.jp/sake/index.php</t>
+        </is>
+      </c>
+      <c r="R39" s="7" t="inlineStr">
+        <is>
+          <t>https://online.kamoizumi.com/?pid=188371835</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>西条エリア7蔵</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>賀茂泉酒造</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>賀茂泉</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="inlineStr"/>
+      <c r="E40" s="9" t="inlineStr">
+        <is>
+          <t>純米吟醸「山吹色の酒」</t>
+        </is>
+      </c>
+      <c r="F40" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G40" s="9" t="inlineStr">
+        <is>
+          <t>公式主要熟成酒</t>
+        </is>
+      </c>
+      <c r="H40" s="9" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I40" s="9" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J40" s="9" t="inlineStr">
+        <is>
+          <t>純米吟醸</t>
+        </is>
+      </c>
+      <c r="K40" s="9" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="L40" s="9" t="inlineStr"/>
+      <c r="M40" s="9" t="inlineStr">
+        <is>
+          <t>常温 / ぬる燗 / ロック</t>
+        </is>
+      </c>
+      <c r="N40" s="9" t="inlineStr">
+        <is>
+          <t>720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="O40" s="9" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="P40" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q40" s="9" t="inlineStr">
+        <is>
+          <t>https://www.kamoizumi.co.jp/sake/index.php</t>
+        </is>
+      </c>
+      <c r="R40" s="9" t="inlineStr">
+        <is>
+          <t>https://www.kamoizumi.co.jp/sake/index.php</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>西条エリア7蔵</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>賀茂泉酒造</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>賀茂泉</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr"/>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>純米酒 一 (はじめ)</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t>公式が入門酒・ウチ飲み定番と明記</t>
+        </is>
+      </c>
+      <c r="H41" s="7" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I41" s="7" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J41" s="7" t="inlineStr">
+        <is>
+          <t>純米</t>
+        </is>
+      </c>
+      <c r="K41" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="L41" s="7" t="inlineStr"/>
+      <c r="M41" s="7" t="inlineStr">
+        <is>
+          <t>冷酒 / ぬる燗 / 燗酒</t>
+        </is>
+      </c>
+      <c r="N41" s="7" t="inlineStr">
+        <is>
+          <t>300ml / 720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="O41" s="7" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="P41" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q41" s="7" t="inlineStr">
+        <is>
+          <t>https://www.kamoizumi.co.jp/sake/index.php</t>
+        </is>
+      </c>
+      <c r="R41" s="7" t="inlineStr">
+        <is>
+          <t>https://online.kamoizumi.com/?pid=188377558</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t>西条エリア7蔵</t>
+        </is>
+      </c>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>賀茂泉酒造</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>賀茂泉</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="inlineStr"/>
+      <c r="E42" s="9" t="inlineStr">
+        <is>
+          <t>造賀純米酒</t>
+        </is>
+      </c>
+      <c r="F42" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G42" s="9" t="inlineStr">
+        <is>
+          <t>東広島造賀地区山田錦を使う地域性の高い定番</t>
+        </is>
+      </c>
+      <c r="H42" s="9" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I42" s="9" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J42" s="9" t="inlineStr">
+        <is>
+          <t>純米</t>
+        </is>
+      </c>
+      <c r="K42" s="9" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="L42" s="9" t="inlineStr"/>
+      <c r="M42" s="9" t="inlineStr">
+        <is>
+          <t>常温 / ぬる燗</t>
+        </is>
+      </c>
+      <c r="N42" s="9" t="inlineStr">
+        <is>
+          <t>720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="O42" s="9" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="P42" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q42" s="9" t="inlineStr">
+        <is>
+          <t>https://kamoizumi.co.jp/sake/index.php</t>
+        </is>
+      </c>
+      <c r="R42" s="9" t="inlineStr">
+        <is>
+          <t>https://online.kamoizumi.com/?pid=188377419</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>西条エリア7蔵</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>賀茂泉酒造</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>賀茂泉</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr"/>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>純米大吟醸「皇寿」</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G43" s="7" t="inlineStr">
+        <is>
+          <t>公式主要高級酒</t>
+        </is>
+      </c>
+      <c r="H43" s="7" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I43" s="7" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J43" s="7" t="inlineStr">
+        <is>
+          <t>純米大吟醸</t>
+        </is>
+      </c>
+      <c r="K43" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="L43" s="7" t="inlineStr"/>
+      <c r="M43" s="7" t="inlineStr">
+        <is>
+          <t>冷酒 / 冷やして / 燗酒</t>
+        </is>
+      </c>
+      <c r="N43" s="7" t="inlineStr">
+        <is>
+          <t>180ml / 300ml / 500ml / 720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="O43" s="7" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="P43" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q43" s="7" t="inlineStr">
+        <is>
+          <t>https://www.kamoizumi.co.jp/sake/index.php</t>
+        </is>
+      </c>
+      <c r="R43" s="7" t="inlineStr">
+        <is>
+          <t>https://online.kamoizumi.com/?pid=188371835</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="9" t="inlineStr">
+        <is>
+          <t>西条エリア7蔵</t>
+        </is>
+      </c>
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>賀茂泉酒造</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>賀茂泉</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="inlineStr"/>
+      <c r="E44" s="9" t="inlineStr">
+        <is>
+          <t>純米大吟醸「延寿」</t>
+        </is>
+      </c>
+      <c r="F44" s="9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G44" s="9" t="inlineStr">
+        <is>
+          <t>公式主要純米大吟醸</t>
+        </is>
+      </c>
+      <c r="H44" s="9" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I44" s="9" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J44" s="9" t="inlineStr">
+        <is>
+          <t>純米大吟醸</t>
+        </is>
+      </c>
+      <c r="K44" s="9" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="L44" s="9" t="inlineStr"/>
+      <c r="M44" s="9" t="inlineStr">
+        <is>
+          <t>冷酒 / 冷やして / 燗酒</t>
+        </is>
+      </c>
+      <c r="N44" s="9" t="inlineStr">
+        <is>
+          <t>180ml / 300ml / 500ml / 720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="O44" s="9" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="P44" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q44" s="9" t="inlineStr">
+        <is>
+          <t>https://www.kamoizumi.co.jp/sake/index.php</t>
+        </is>
+      </c>
+      <c r="R44" s="9" t="inlineStr">
+        <is>
+          <t>https://online.kamoizumi.com/?pid=188371835</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>西条エリア7蔵</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>賀茂泉酒造</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>ROCK HOPPER</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr"/>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>純米吟醸生原酒 ROCK HOPPER</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>公式現行生原酒シリーズ</t>
+        </is>
+      </c>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I45" s="7" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J45" s="7" t="inlineStr">
+        <is>
+          <t>純米吟醸</t>
+        </is>
+      </c>
+      <c r="K45" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="L45" s="7" t="inlineStr"/>
+      <c r="M45" s="7" t="inlineStr">
+        <is>
+          <t>ロック</t>
+        </is>
+      </c>
+      <c r="N45" s="7" t="inlineStr">
+        <is>
+          <t>720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="O45" s="7" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="P45" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q45" s="7" t="inlineStr">
+        <is>
+          <t>https://www.kamoizumi.co.jp/sake/index.php</t>
+        </is>
+      </c>
+      <c r="R45" s="7" t="inlineStr">
+        <is>
+          <t>https://www.kamoizumi.co.jp/sake/index.php</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="9" t="inlineStr">
+        <is>
+          <t>西条エリア7蔵</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="inlineStr">
+        <is>
           <t>山陽鶴酒造</t>
         </is>
       </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>山陽鶴</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="inlineStr"/>
+      <c r="E46" s="9" t="inlineStr">
+        <is>
+          <t>純米大吟醸 KUBO</t>
+        </is>
+      </c>
+      <c r="F46" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G46" s="9" t="inlineStr">
+        <is>
+          <t>現行通年返礼品・代表高級酒</t>
+        </is>
+      </c>
+      <c r="H46" s="9" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I46" s="9" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J46" s="9" t="inlineStr">
+        <is>
+          <t>純米大吟醸</t>
+        </is>
+      </c>
+      <c r="K46" s="9" t="inlineStr">
+        <is>
+          <t>辛口</t>
+        </is>
+      </c>
+      <c r="L46" s="9" t="inlineStr">
+        <is>
+          <t>+4</t>
+        </is>
+      </c>
+      <c r="M46" s="9" t="inlineStr">
+        <is>
+          <t>冷酒</t>
+        </is>
+      </c>
+      <c r="N46" s="9" t="inlineStr">
+        <is>
+          <t>720ml</t>
+        </is>
+      </c>
+      <c r="O46" s="9" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="P46" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q46" s="9" t="inlineStr">
+        <is>
+          <t>https://www.furusato.aeon.co.jp/gift-in-return/aaa72316281ae6d75280fb28cb3cae46/</t>
+        </is>
+      </c>
+      <c r="R46" s="9" t="inlineStr">
+        <is>
+          <t>https://www.furusato.aeon.co.jp/gift-in-return/aaa72316281ae6d75280fb28cb3cae46/</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>西条エリア7蔵</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>山陽鶴酒造</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>山陽鶴</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr"/>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>大吟醸 ほんと</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G47" s="7" t="inlineStr">
+        <is>
+          <t>現行地域製品DBで販売場所掲載の代表大吟醸</t>
+        </is>
+      </c>
+      <c r="H47" s="7" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I47" s="7" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J47" s="7" t="inlineStr">
+        <is>
+          <t>大吟醸</t>
+        </is>
+      </c>
+      <c r="K47" s="7" t="inlineStr">
+        <is>
+          <t>やや辛口</t>
+        </is>
+      </c>
+      <c r="L47" s="7" t="inlineStr">
+        <is>
+          <t>+4</t>
+        </is>
+      </c>
+      <c r="M47" s="7" t="inlineStr">
+        <is>
+          <t>冷酒 / 常温</t>
+        </is>
+      </c>
+      <c r="N47" s="7" t="inlineStr">
+        <is>
+          <t>720ml</t>
+        </is>
+      </c>
+      <c r="O47" s="7" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="P47" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q47" s="7" t="inlineStr">
+        <is>
+          <t>https://www.buyhiro.com/database/products/products_0549/</t>
+        </is>
+      </c>
+      <c r="R47" s="7" t="inlineStr">
+        <is>
+          <t>https://www.buyhiro.com/database/products/products_0549/</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="9" t="inlineStr">
+        <is>
+          <t>西条エリア7蔵</t>
+        </is>
+      </c>
+      <c r="B48" s="9" t="inlineStr">
+        <is>
+          <t>山陽鶴酒造</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>山陽鶴</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="inlineStr"/>
+      <c r="E48" s="9" t="inlineStr">
+        <is>
+          <t>純米吟醸</t>
+        </is>
+      </c>
+      <c r="F48" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G48" s="9" t="inlineStr">
+        <is>
+          <t>公式五酒セットで「代表的なお酒」と明記</t>
+        </is>
+      </c>
+      <c r="H48" s="9" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I48" s="9" t="inlineStr">
+        <is>
+          <t>個別SKU未確認</t>
+        </is>
+      </c>
+      <c r="J48" s="9" t="inlineStr">
+        <is>
+          <t>純米吟醸</t>
+        </is>
+      </c>
+      <c r="K48" s="9" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="L48" s="9" t="inlineStr"/>
+      <c r="M48" s="9" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N48" s="9" t="inlineStr"/>
+      <c r="O48" s="9" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="P48" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q48" s="9" t="inlineStr">
+        <is>
+          <t>https://sanyotsuru.jp/archives/product/gosyu</t>
+        </is>
+      </c>
+      <c r="R48" s="9" t="inlineStr">
+        <is>
+          <t>https://sanyotsuru.jp/archives/product/gosyu</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>西条エリア7蔵</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>山陽鶴酒造</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>山陽鶴</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr"/>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>本醸造</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G49" s="7" t="inlineStr">
+        <is>
+          <t>公式五酒セットで「代表的なお酒」と明記</t>
+        </is>
+      </c>
+      <c r="H49" s="7" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I49" s="7" t="inlineStr">
+        <is>
+          <t>個別SKU未確認</t>
+        </is>
+      </c>
+      <c r="J49" s="7" t="inlineStr">
+        <is>
+          <t>本醸造</t>
+        </is>
+      </c>
+      <c r="K49" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="L49" s="7" t="inlineStr"/>
+      <c r="M49" s="7" t="inlineStr">
+        <is>
+          <t>冷酒 / 常温 / 燗酒</t>
+        </is>
+      </c>
+      <c r="N49" s="7" t="inlineStr"/>
+      <c r="O49" s="7" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="P49" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q49" s="7" t="inlineStr">
+        <is>
+          <t>https://sanyotsuru.jp/archives/product/gosyu</t>
+        </is>
+      </c>
+      <c r="R49" s="7" t="inlineStr">
+        <is>
+          <t>https://sanyotsuru.jp/archives/product/gosyu</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="9" t="inlineStr">
+        <is>
+          <t>西条エリア7蔵</t>
+        </is>
+      </c>
+      <c r="B50" s="9" t="inlineStr">
+        <is>
+          <t>山陽鶴酒造</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>山陽鶴</t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="inlineStr"/>
+      <c r="E50" s="9" t="inlineStr">
+        <is>
+          <t>上撰</t>
+        </is>
+      </c>
+      <c r="F50" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G50" s="9" t="inlineStr">
+        <is>
+          <t>公式五酒セットで「代表的なお酒」と明記</t>
+        </is>
+      </c>
+      <c r="H50" s="9" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I50" s="9" t="inlineStr">
+        <is>
+          <t>個別SKU未確認</t>
+        </is>
+      </c>
+      <c r="J50" s="9" t="inlineStr">
+        <is>
+          <t>普通酒・上撰</t>
+        </is>
+      </c>
+      <c r="K50" s="9" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="L50" s="9" t="inlineStr"/>
+      <c r="M50" s="9" t="inlineStr">
+        <is>
+          <t>常温 / 熱燗（提供例）</t>
+        </is>
+      </c>
+      <c r="N50" s="9" t="inlineStr"/>
+      <c r="O50" s="9" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="P50" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="Q50" s="9" t="inlineStr">
+        <is>
+          <t>https://sanyotsuru.jp/archives/product/gosyu</t>
+        </is>
+      </c>
+      <c r="R50" s="9" t="inlineStr">
+        <is>
+          <t>https://sanyotsuru.jp/archives/product/gosyu</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:R50"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:R2"/>
+    <mergeCell ref="A1:R1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M39"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="46" customWidth="1" min="12" max="12"/>
+    <col width="42" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>東広島市 西条エリア7蔵 主要日本酒一覧</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>各蔵Aランク5銘柄。売上順位ではなく、蔵元推奨・代表性・現行流通を優先。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>酒蔵</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>ブランド</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>シリーズ</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>商品名</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>分類</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>甘辛目安</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>日本酒度</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>おすすめの飲み方</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>容量</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>流通区分</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>SKU確認</t>
+        </is>
+      </c>
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>選定理由</t>
+        </is>
+      </c>
+      <c r="M4" s="6" t="inlineStr">
+        <is>
+          <t>出典URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>賀茂鶴酒造</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>賀茂鶴</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr"/>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>大吟醸 特製ゴールド賀茂鶴</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>大吟醸</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr"/>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>冷酒 / 燗酒</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>180ml / 300ml / 720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="K5" s="7" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>公式直近1年販売本数ベース晩酌1位・賀茂鶴を代表する銘柄</t>
+        </is>
+      </c>
+      <c r="M5" s="8" t="inlineStr">
+        <is>
+          <t>https://shop.kamotsuru.jp/SHOP/GK-A2.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>賀茂鶴酒造</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>賀茂鶴</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr"/>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>純米吟醸 一滴入魂</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>純米吟醸</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr"/>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>冷酒 / ぬる燗 / 燗酒</t>
+        </is>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>300ml / 720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="J6" s="9" t="inlineStr">
+        <is>
+          <t>限定流通</t>
+        </is>
+      </c>
+      <c r="K6" s="9" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="L6" s="9" t="inlineStr">
+        <is>
+          <t>公式晩酌おすすめ2位・アジア圏で人気</t>
+        </is>
+      </c>
+      <c r="M6" s="8" t="inlineStr">
+        <is>
+          <t>https://shop.kamotsuru.jp/SHOP/GP-A1.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>賀茂鶴酒造</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>酒中在心</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr"/>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>酒中在心 橙 純米吟醸 生もと 八反35号</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>純米吟醸</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr"/>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>冷酒 / 常温 / ぬる燗 / 燗酒</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>限定流通</t>
+        </is>
+      </c>
+      <c r="K7" s="7" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>公式晩酌おすすめ3位・販路限定の主要シリーズ</t>
+        </is>
+      </c>
+      <c r="M7" s="8" t="inlineStr">
+        <is>
+          <t>https://shop.kamotsuru.jp/SHOP/shutyuzaishin-daidai_1800.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>賀茂鶴酒造</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>賀茂鶴</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr"/>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>本醸造 からくち</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>本醸造</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr"/>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>冷酒 / 燗酒</t>
+        </is>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>180ml / 300ml / 720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="K8" s="9" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="L8" s="9" t="inlineStr">
+        <is>
+          <t>公式晩酌おすすめ4位・料飲店人気の食中酒</t>
+        </is>
+      </c>
+      <c r="M8" s="8" t="inlineStr">
+        <is>
+          <t>https://shop.kamotsuru.jp/SHOP/honkara1800.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>賀茂鶴酒造</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>賀茂鶴</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr"/>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>特別本醸造 超特撰特等酒</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>特別本醸造</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr"/>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>冷酒 / ぬる燗 / 燗酒</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>300ml / 720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="K9" s="7" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="L9" s="7" t="inlineStr">
+        <is>
+          <t>公式晩酌おすすめ5位・長年の定番</t>
+        </is>
+      </c>
+      <c r="M9" s="8" t="inlineStr">
+        <is>
+          <t>https://shop.kamotsuru.jp/SHOP/tokutou1800.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>白牡丹酒造</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>白牡丹</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr"/>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>大吟醸</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>大吟醸</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>やや辛口</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>+3</t>
+        </is>
+      </c>
+      <c r="H10" s="9" t="inlineStr">
+        <is>
+          <t>常温 / 冷酒</t>
+        </is>
+      </c>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>300ml / 720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="J10" s="9" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="K10" s="9" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="L10" s="9" t="inlineStr">
+        <is>
+          <t>公式現行定番・300/720/1800ml展開</t>
+        </is>
+      </c>
+      <c r="M10" s="8" t="inlineStr">
+        <is>
+          <t>https://www.hakubotan.co.jp/products/</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>白牡丹酒造</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>白牡丹</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr"/>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>純米吟醸</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>純米吟醸</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>中口</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>+0.5</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>常温</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>限定流通</t>
+        </is>
+      </c>
+      <c r="K11" s="7" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="L11" s="7" t="inlineStr">
+        <is>
+          <t>公式現行定番・ワイングラスアワード受賞</t>
+        </is>
+      </c>
+      <c r="M11" s="8" t="inlineStr">
+        <is>
+          <t>https://www.hakubotan.co.jp/products/%e3%80%90%e6%97%a5%e6%9c%ac%e9%85%92-%e7%99%bd%e7%89%a1%e4%b8%b9%e3%80%91%e7%b4%94%e7%b1%b3%e5%90%9f%e9%86%b8-1-8l%e7%93%b6%e8%a9%b0/</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>白牡丹酒造</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>白牡丹</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr"/>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>純米酒</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>純米</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>中口</t>
+        </is>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>+0.5</t>
+        </is>
+      </c>
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>常温 / ぬる燗 / 熱燗 / 燗酒</t>
+        </is>
+      </c>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>300ml / 720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="J12" s="9" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="K12" s="9" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="L12" s="9" t="inlineStr">
+        <is>
+          <t>公式定番・燗酒コンテスト受賞</t>
+        </is>
+      </c>
+      <c r="M12" s="8" t="inlineStr">
+        <is>
+          <t>https://www.hakubotan.co.jp/products/%e3%80%90%e6%97%a5%e6%9c%ac%e9%85%92-%e7%99%bd%e7%89%a1%e4%b8%b9%e3%80%91%e7%b4%94%e7%b1%b3%e9%85%92-1-8l%e7%93%b6%e8%a9%b0/</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>白牡丹酒造</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>白牡丹</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>万年蔵</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>純米大吟醸 原酒 万年蔵 杜氏 鹿島正</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>純米大吟醸</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>甘口</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>-8</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>常温 / ぬる燗 / 燗酒</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="L13" s="7" t="inlineStr">
+        <is>
+          <t>公式高級ライン・広島らしさを前面に出す商品</t>
+        </is>
+      </c>
+      <c r="M13" s="8" t="inlineStr">
+        <is>
+          <t>https://www.hakubotan.co.jp/products/%e3%80%90%e6%97%a5%e6%9c%ac%e9%85%92-%e7%99%bd%e7%89%a1%e4%b8%b9%e3%80%91%e7%b4%94%e7%b1%b3%e5%a4%a7%e5%90%9f%e9%86%b8-%e5%8e%9f%e9%85%92-%e4%b8%87%e5%b9%b4%e8%94%b5-%e6%9d%9c%e6%b0%8f-%e9%b9%bf/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>白牡丹酒造</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>白牡丹</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>Paeon</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>Paeon(ピオン)</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>特別純米</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>やや甘口</t>
+        </is>
+      </c>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>-1.5</t>
+        </is>
+      </c>
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t>常温 / 冷酒</t>
+        </is>
+      </c>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>500ml</t>
+        </is>
+      </c>
+      <c r="J14" s="9" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="K14" s="9" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="L14" s="9" t="inlineStr">
+        <is>
+          <t>ワイングラスでおいしい日本酒アワード2026最高金賞</t>
+        </is>
+      </c>
+      <c r="M14" s="8" t="inlineStr">
+        <is>
+          <t>https://www.hakubotan.co.jp/products/%E3%80%90%E6%97%A5%E6%9C%AC%E9%85%92-%E7%99%BD%E7%89%A1%E4%B8%B9%E3%80%91paeon%E3%83%94%E3%82%AA%E3%83%B3%E3%80%90%E6%96%B0%E3%80%91/</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>西條鶴醸造</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>西條鶴</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr"/>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>純米大吟醸原酒「神髄」</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>純米大吟醸</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr"/>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>常温</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>180ml / 500ml / 720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="K15" s="7" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="L15" s="7" t="inlineStr">
+        <is>
+          <t>公式おすすめ・純米大吟醸の中心商品</t>
+        </is>
+      </c>
+      <c r="M15" s="8" t="inlineStr">
+        <is>
+          <t>https://saijotsuru.co.jp/?pid=180817561</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>西條鶴醸造</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>西條鶴</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr"/>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>辛口純米酒『きんさいや』</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>純米</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>辛口</t>
+        </is>
+      </c>
+      <c r="G16" s="9" t="inlineStr"/>
+      <c r="H16" s="9" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t>500ml</t>
+        </is>
+      </c>
+      <c r="J16" s="9" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="K16" s="9" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="L16" s="9" t="inlineStr">
+        <is>
+          <t>公式おすすめ商品</t>
+        </is>
+      </c>
+      <c r="M16" s="8" t="inlineStr">
+        <is>
+          <t>https://saijotsuru.co.jp/?pid=189850838</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>西條鶴醸造</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>西條鶴</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr"/>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>純米酒「大地の風」</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>純米</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr"/>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>冷酒 / 常温 / 熱燗</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="K17" s="7" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="L17" s="7" t="inlineStr">
+        <is>
+          <t>公式おすすめ・定番純米</t>
+        </is>
+      </c>
+      <c r="M17" s="8" t="inlineStr">
+        <is>
+          <t>https://saijotsuru.co.jp/?pid=157617524</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>西條鶴醸造</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>西條鶴</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr"/>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>純米吟醸「大地の冠」</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>純米吟醸</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="G18" s="9" t="inlineStr"/>
+      <c r="H18" s="9" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="J18" s="9" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="K18" s="9" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="L18" s="9" t="inlineStr">
+        <is>
+          <t>公式おすすめ・定番純米吟醸</t>
+        </is>
+      </c>
+      <c r="M18" s="8" t="inlineStr">
+        <is>
+          <t>https://saijotsuru.co.jp/?pid=157617368</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>西條鶴醸造</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>西條鶴</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr"/>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>吟醸酒「ゴールド西條鶴」</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>吟醸</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr"/>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>冷酒 / 常温 / ぬる燗</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>720ml</t>
+        </is>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="K19" s="7" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="L19" s="7" t="inlineStr">
+        <is>
+          <t>公式贈答・おすすめ定番</t>
+        </is>
+      </c>
+      <c r="M19" s="8" t="inlineStr">
+        <is>
+          <t>https://saijotsuru.co.jp/?pid=157617449</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>亀齢酒造</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>亀齢</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr"/>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>亀齢 辛口純米 八拾</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>純米</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>辛口</t>
+        </is>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>＋５</t>
+        </is>
+      </c>
+      <c r="H20" s="9" t="inlineStr">
+        <is>
+          <t>燗酒</t>
+        </is>
+      </c>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="J20" s="9" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="K20" s="9" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="L20" s="9" t="inlineStr">
+        <is>
+          <t>現行流通で代表銘柄として広く扱われる辛口純米</t>
+        </is>
+      </c>
+      <c r="M20" s="8" t="inlineStr">
+        <is>
+          <t>https://www.hiroshimasake.com/product/37</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>亀齢酒造</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>亀齢</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr"/>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>亀齢 大吟醸 創</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>大吟醸</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>辛口</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>＋５</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>燗酒</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>720ml</t>
+        </is>
+      </c>
+      <c r="J21" s="7" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="K21" s="7" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="L21" s="7" t="inlineStr">
+        <is>
+          <t>現行流通の代表高級酒</t>
+        </is>
+      </c>
+      <c r="M21" s="8" t="inlineStr">
+        <is>
+          <t>https://www.hiroshimasake.com/product/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>亀齢酒造</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>亀齢萬年</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr"/>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>亀齢萬年 純米大吟醸原酒五拾 生酒</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>純米大吟醸</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="G22" s="9" t="inlineStr"/>
+      <c r="H22" s="9" t="inlineStr">
+        <is>
+          <t>燗酒</t>
+        </is>
+      </c>
+      <c r="I22" s="9" t="inlineStr">
+        <is>
+          <t>720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="J22" s="9" t="inlineStr">
+        <is>
+          <t>季節商品</t>
+        </is>
+      </c>
+      <c r="K22" s="9" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="L22" s="9" t="inlineStr">
+        <is>
+          <t>亀齢萬年を代表する2026年現行の純米大吟醸ライン</t>
+        </is>
+      </c>
+      <c r="M22" s="8" t="inlineStr">
+        <is>
+          <t>https://www.hiroshimasake.com/product/552</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>亀齢酒造</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>亀齢</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr"/>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>亀齢 純米吟醸 六拾</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>純米吟醸</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr"/>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>720ml</t>
+        </is>
+      </c>
+      <c r="J23" s="7" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="K23" s="7" t="inlineStr">
+        <is>
+          <t>個別SKU未確認</t>
+        </is>
+      </c>
+      <c r="L23" s="7" t="inlineStr">
+        <is>
+          <t>2026年東広島10蔵定期便採用の現行純米吟醸</t>
+        </is>
+      </c>
+      <c r="M23" s="8" t="inlineStr">
+        <is>
+          <t>https://e-sake.jp/article/article-1369/</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>亀齢酒造</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>亀齢</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr"/>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>亀齢 上撰</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>普通酒・上撰</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>辛口</t>
+        </is>
+      </c>
+      <c r="G24" s="9" t="inlineStr"/>
+      <c r="H24" s="9" t="inlineStr">
+        <is>
+          <t>冷酒 / 燗酒</t>
+        </is>
+      </c>
+      <c r="I24" s="9" t="inlineStr">
+        <is>
+          <t>1,800ml</t>
+        </is>
+      </c>
+      <c r="J24" s="9" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="K24" s="9" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="L24" s="9" t="inlineStr">
+        <is>
+          <t>地元で継続流通する定番酒</t>
+        </is>
+      </c>
+      <c r="M24" s="8" t="inlineStr">
+        <is>
+          <t>https://osake-style.com/SHOP/11012948.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>福美人酒造</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>福美人</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr"/>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>大吟醸 蔵乃華 （ くらのはな ）</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>大吟醸</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>やや辛口</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>+2.0</t>
+        </is>
+      </c>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>常温 / 冷酒</t>
+        </is>
+      </c>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="J25" s="7" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="K25" s="7" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="L25" s="7" t="inlineStr">
+        <is>
+          <t>公式が代表的商品として掲載する上位酒</t>
+        </is>
+      </c>
+      <c r="M25" s="8" t="inlineStr">
+        <is>
+          <t>https://www.fukubijin.co.jp/SHOP/1020.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>福美人酒造</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>福美人</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr"/>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>大吟醸 西條酒造学校</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>大吟醸</t>
+        </is>
+      </c>
+      <c r="F26" s="9" t="inlineStr">
+        <is>
+          <t>やや辛口</t>
+        </is>
+      </c>
+      <c r="G26" s="9" t="inlineStr">
+        <is>
+          <t>+3.0</t>
+        </is>
+      </c>
+      <c r="H26" s="9" t="inlineStr">
+        <is>
+          <t>冷酒 / 常温</t>
+        </is>
+      </c>
+      <c r="I26" s="9" t="inlineStr">
+        <is>
+          <t>720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="J26" s="9" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="K26" s="9" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="L26" s="9" t="inlineStr">
+        <is>
+          <t>蔵の歴史を体現する代表商品</t>
+        </is>
+      </c>
+      <c r="M26" s="8" t="inlineStr">
+        <is>
+          <t>https://www.fukubijin.co.jp/SHOP/1120.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>福美人酒造</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>福美人</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr"/>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>純米吟醸</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>純米吟醸</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>辛口</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>+4.0</t>
+        </is>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>燗酒</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="J27" s="7" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="K27" s="7" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="L27" s="7" t="inlineStr">
+        <is>
+          <t>公式が代表的商品として掲載する定番</t>
+        </is>
+      </c>
+      <c r="M27" s="8" t="inlineStr">
+        <is>
+          <t>https://www.fukubijin.co.jp/SHOP/1221.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>福美人酒造</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>福美人</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr"/>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>純米酒</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>純米</t>
+        </is>
+      </c>
+      <c r="F28" s="9" t="inlineStr">
+        <is>
+          <t>やや辛口</t>
+        </is>
+      </c>
+      <c r="G28" s="9" t="inlineStr">
+        <is>
+          <t>+3.0</t>
+        </is>
+      </c>
+      <c r="H28" s="9" t="inlineStr">
+        <is>
+          <t>燗酒</t>
+        </is>
+      </c>
+      <c r="I28" s="9" t="inlineStr">
+        <is>
+          <t>720ml</t>
+        </is>
+      </c>
+      <c r="J28" s="9" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="K28" s="9" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="L28" s="9" t="inlineStr">
+        <is>
+          <t>現行定番純米</t>
+        </is>
+      </c>
+      <c r="M28" s="8" t="inlineStr">
+        <is>
+          <t>https://www.fukubijin.co.jp/SHOP/2020.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>福美人酒造</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>福美人</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr"/>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>上撰</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>普通酒・上撰</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="inlineStr"/>
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>720ml</t>
+        </is>
+      </c>
+      <c r="J29" s="7" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="K29" s="7" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="L29" s="7" t="inlineStr">
+        <is>
+          <t>公式が代表的商品として掲載する定番酒</t>
+        </is>
+      </c>
+      <c r="M29" s="8" t="inlineStr">
+        <is>
+          <t>https://www.fukubijin.co.jp/SHOP/2230.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>賀茂泉酒造</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>賀茂泉</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr"/>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>純米吟醸「朱泉本仕込」</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>純米吟醸</t>
+        </is>
+      </c>
+      <c r="F30" s="9" t="inlineStr">
+        <is>
+          <t>中口</t>
+        </is>
+      </c>
+      <c r="G30" s="9" t="inlineStr">
+        <is>
+          <t>+1.0</t>
+        </is>
+      </c>
+      <c r="H30" s="9" t="inlineStr">
+        <is>
+          <t>常温 / ぬる燗 / ロック</t>
+        </is>
+      </c>
+      <c r="I30" s="9" t="inlineStr">
+        <is>
+          <t>180ml / 720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="J30" s="9" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="K30" s="9" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="L30" s="9" t="inlineStr">
+        <is>
+          <t>公式が「賀茂泉を代表するお酒」と明記</t>
+        </is>
+      </c>
+      <c r="M30" s="8" t="inlineStr">
+        <is>
+          <t>https://www.kamoizumi.co.jp/sake/index.php</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>賀茂泉酒造</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>賀茂泉</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr"/>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>純米大吟醸「壽」</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>純米大吟醸</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="inlineStr"/>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>冷酒 / 冷やして / 燗酒</t>
+        </is>
+      </c>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="J31" s="7" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="K31" s="7" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="L31" s="7" t="inlineStr">
+        <is>
+          <t>公式が醸造技術の極み・究極のお酒と説明</t>
+        </is>
+      </c>
+      <c r="M31" s="8" t="inlineStr">
+        <is>
+          <t>https://online.kamoizumi.com/?pid=188371835</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>賀茂泉酒造</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>賀茂泉</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr"/>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>純米吟醸「山吹色の酒」</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="inlineStr">
+        <is>
+          <t>純米吟醸</t>
+        </is>
+      </c>
+      <c r="F32" s="9" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="G32" s="9" t="inlineStr"/>
+      <c r="H32" s="9" t="inlineStr">
+        <is>
+          <t>常温 / ぬる燗 / ロック</t>
+        </is>
+      </c>
+      <c r="I32" s="9" t="inlineStr">
+        <is>
+          <t>720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="J32" s="9" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="K32" s="9" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="L32" s="9" t="inlineStr">
+        <is>
+          <t>公式主要熟成酒</t>
+        </is>
+      </c>
+      <c r="M32" s="8" t="inlineStr">
+        <is>
+          <t>https://www.kamoizumi.co.jp/sake/index.php</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>賀茂泉酒造</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>賀茂泉</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr"/>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>純米酒 一 (はじめ)</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>純米</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="G33" s="7" t="inlineStr"/>
+      <c r="H33" s="7" t="inlineStr">
+        <is>
+          <t>冷酒 / ぬる燗 / 燗酒</t>
+        </is>
+      </c>
+      <c r="I33" s="7" t="inlineStr">
+        <is>
+          <t>300ml / 720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="J33" s="7" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="K33" s="7" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="L33" s="7" t="inlineStr">
+        <is>
+          <t>公式が入門酒・ウチ飲み定番と明記</t>
+        </is>
+      </c>
+      <c r="M33" s="8" t="inlineStr">
+        <is>
+          <t>https://online.kamoizumi.com/?pid=188377558</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>賀茂泉酒造</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>賀茂泉</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr"/>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>造賀純米酒</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>純米</t>
+        </is>
+      </c>
+      <c r="F34" s="9" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="G34" s="9" t="inlineStr"/>
+      <c r="H34" s="9" t="inlineStr">
+        <is>
+          <t>常温 / ぬる燗</t>
+        </is>
+      </c>
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>720ml / 1,800ml</t>
+        </is>
+      </c>
+      <c r="J34" s="9" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="K34" s="9" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="L34" s="9" t="inlineStr">
+        <is>
+          <t>東広島造賀地区山田錦を使う地域性の高い定番</t>
+        </is>
+      </c>
+      <c r="M34" s="8" t="inlineStr">
+        <is>
+          <t>https://online.kamoizumi.com/?pid=188377419</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>山陽鶴酒造</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>山陽鶴</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr"/>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>純米大吟醸 KUBO</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>純米大吟醸</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>辛口</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>+4</t>
+        </is>
+      </c>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>冷酒</t>
+        </is>
+      </c>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>720ml</t>
+        </is>
+      </c>
+      <c r="J35" s="7" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="K35" s="7" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="L35" s="7" t="inlineStr">
+        <is>
+          <t>現行通年返礼品・代表高級酒</t>
+        </is>
+      </c>
+      <c r="M35" s="8" t="inlineStr">
+        <is>
+          <t>https://www.furusato.aeon.co.jp/gift-in-return/aaa72316281ae6d75280fb28cb3cae46/</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>山陽鶴酒造</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>山陽鶴</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr"/>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>大吟醸 ほんと</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="inlineStr">
+        <is>
+          <t>大吟醸</t>
+        </is>
+      </c>
+      <c r="F36" s="9" t="inlineStr">
+        <is>
+          <t>やや辛口</t>
+        </is>
+      </c>
+      <c r="G36" s="9" t="inlineStr">
+        <is>
+          <t>+4</t>
+        </is>
+      </c>
+      <c r="H36" s="9" t="inlineStr">
+        <is>
+          <t>冷酒 / 常温</t>
+        </is>
+      </c>
+      <c r="I36" s="9" t="inlineStr">
+        <is>
+          <t>720ml</t>
+        </is>
+      </c>
+      <c r="J36" s="9" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="K36" s="9" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="L36" s="9" t="inlineStr">
+        <is>
+          <t>現行地域製品DBで販売場所掲載の代表大吟醸</t>
+        </is>
+      </c>
+      <c r="M36" s="8" t="inlineStr">
+        <is>
+          <t>https://www.buyhiro.com/database/products/products_0549/</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>山陽鶴酒造</t>
+        </is>
+      </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
+          <t>山陽鶴</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr"/>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
           <t>純米吟醸</t>
         </is>
       </c>
-      <c r="C37" s="7" t="inlineStr">
+      <c r="E37" s="7" t="inlineStr">
         <is>
           <t>純米吟醸</t>
         </is>
       </c>
-      <c r="D37" s="7" t="inlineStr">
+      <c r="F37" s="7" t="inlineStr">
         <is>
           <t>不明</t>
-        </is>
-      </c>
-      <c r="E37" s="7" t="inlineStr"/>
-      <c r="F37" s="7" t="inlineStr">
-        <is>
-          <t>要確認</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr"/>
       <c r="H37" s="7" t="inlineStr">
         <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I37" s="7" t="inlineStr"/>
+      <c r="J37" s="7" t="inlineStr">
+        <is>
           <t>一般流通</t>
         </is>
       </c>
-      <c r="I37" s="7" t="inlineStr">
-        <is>
-          <t>現行流通・純米吟醸枠／定番性と酒質の幅を考慮</t>
-        </is>
-      </c>
-      <c r="J37" s="8" t="inlineStr">
+      <c r="K37" s="7" t="inlineStr">
+        <is>
+          <t>個別SKU未確認</t>
+        </is>
+      </c>
+      <c r="L37" s="7" t="inlineStr">
+        <is>
+          <t>公式五酒セットで「代表的なお酒」と明記</t>
+        </is>
+      </c>
+      <c r="M37" s="8" t="inlineStr">
         <is>
           <t>https://sanyotsuru.jp/archives/product/gosyu</t>
         </is>
@@ -2415,37 +7487,48 @@
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
+          <t>山陽鶴</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr"/>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
           <t>本醸造</t>
         </is>
       </c>
-      <c r="C38" s="9" t="inlineStr">
+      <c r="E38" s="9" t="inlineStr">
         <is>
           <t>本醸造</t>
         </is>
       </c>
-      <c r="D38" s="9" t="inlineStr">
+      <c r="F38" s="9" t="inlineStr">
         <is>
           <t>不明</t>
-        </is>
-      </c>
-      <c r="E38" s="9" t="inlineStr"/>
-      <c r="F38" s="9" t="inlineStr">
-        <is>
-          <t>冷酒 / 常温 / 燗酒</t>
         </is>
       </c>
       <c r="G38" s="9" t="inlineStr"/>
       <c r="H38" s="9" t="inlineStr">
         <is>
+          <t>冷酒 / 常温 / 燗酒</t>
+        </is>
+      </c>
+      <c r="I38" s="9" t="inlineStr"/>
+      <c r="J38" s="9" t="inlineStr">
+        <is>
           <t>一般流通</t>
         </is>
       </c>
-      <c r="I38" s="9" t="inlineStr">
-        <is>
-          <t>現行流通・本醸造枠／定番性と酒質の幅を考慮</t>
-        </is>
-      </c>
-      <c r="J38" s="8" t="inlineStr">
+      <c r="K38" s="9" t="inlineStr">
+        <is>
+          <t>個別SKU未確認</t>
+        </is>
+      </c>
+      <c r="L38" s="9" t="inlineStr">
+        <is>
+          <t>公式五酒セットで「代表的なお酒」と明記</t>
+        </is>
+      </c>
+      <c r="M38" s="8" t="inlineStr">
         <is>
           <t>https://sanyotsuru.jp/archives/product/gosyu</t>
         </is>
@@ -2459,84 +7542,95 @@
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
+          <t>山陽鶴</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr"/>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
           <t>上撰</t>
         </is>
       </c>
-      <c r="C39" s="7" t="inlineStr">
+      <c r="E39" s="7" t="inlineStr">
         <is>
           <t>普通酒・上撰</t>
         </is>
       </c>
-      <c r="D39" s="7" t="inlineStr">
+      <c r="F39" s="7" t="inlineStr">
         <is>
           <t>不明</t>
-        </is>
-      </c>
-      <c r="E39" s="7" t="inlineStr"/>
-      <c r="F39" s="7" t="inlineStr">
-        <is>
-          <t>常温 / 熱燗（提供例）</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr"/>
       <c r="H39" s="7" t="inlineStr">
         <is>
+          <t>常温 / 熱燗（提供例）</t>
+        </is>
+      </c>
+      <c r="I39" s="7" t="inlineStr"/>
+      <c r="J39" s="7" t="inlineStr">
+        <is>
           <t>一般流通</t>
         </is>
       </c>
-      <c r="I39" s="7" t="inlineStr">
-        <is>
-          <t>現行流通・普通酒・上撰枠／定番性と酒質の幅を考慮</t>
-        </is>
-      </c>
-      <c r="J39" s="8" t="inlineStr">
+      <c r="K39" s="7" t="inlineStr">
+        <is>
+          <t>個別SKU未確認</t>
+        </is>
+      </c>
+      <c r="L39" s="7" t="inlineStr">
+        <is>
+          <t>公式五酒セットで「代表的なお酒」と明記</t>
+        </is>
+      </c>
+      <c r="M39" s="8" t="inlineStr">
         <is>
           <t>https://sanyotsuru.jp/archives/product/gosyu</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J39"/>
+  <autoFilter ref="A4:M39"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A1:M1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J36" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M14" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M16" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M17" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M19" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M20" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M21" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M22" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M23" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M24" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M25" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M26" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M27" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M28" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M29" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M30" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M31" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M32" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M33" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M34" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M35" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M36" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M37" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M38" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M39" r:id="rId35"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -2545,7 +7639,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/東広島市_西条エリア7蔵_主要日本酒一覧.xlsx
+++ b/東広島市_西条エリア7蔵_主要日本酒一覧.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ブランド一覧'!$A$4:$H$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ブランド・中核銘柄'!$A$4:$R$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ブランド・中核銘柄'!$A$4:$R$56</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'主要銘柄'!$A$4:$M$39</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'選定基準'!$A$4:$B$9</definedName>
   </definedNames>
@@ -209,7 +209,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T_593330" displayName="T_593330" ref="A4:H16" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T_268816" displayName="T_268816" ref="A4:H16" headerRowCount="1">
   <autoFilter ref="A4:H16"/>
   <tableColumns count="8">
     <tableColumn id="1" name="エリア"/>
@@ -226,8 +226,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T_934440" displayName="T_934440" ref="A4:R50" headerRowCount="1">
-  <autoFilter ref="A4:R50"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T_69142" displayName="T_69142" ref="A4:R56" headerRowCount="1">
+  <autoFilter ref="A4:R56"/>
   <tableColumns count="18">
     <tableColumn id="1" name="エリア"/>
     <tableColumn id="2" name="酒蔵"/>
@@ -253,7 +253,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="T_671225" displayName="T_671225" ref="A4:M39" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="T_266213" displayName="T_266213" ref="A4:M39" headerRowCount="1">
   <autoFilter ref="A4:M39"/>
   <tableColumns count="13">
     <tableColumn id="1" name="酒蔵"/>
@@ -275,7 +275,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="T_930275" displayName="T_930275" ref="A4:B9" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="T_560804" displayName="T_560804" ref="A4:B9" headerRowCount="1">
   <autoFilter ref="A4:B9"/>
   <tableColumns count="2">
     <tableColumn id="1" name="基準"/>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
         <v>18</v>
@@ -852,11 +852,11 @@
         <v>4</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -890,11 +890,11 @@
         <v>1</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -932,7 +932,7 @@
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -970,7 +970,7 @@
       </c>
       <c r="H8" s="9" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -1297,7 +1297,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R50"/>
+  <dimension ref="A1:R56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="P5" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q5" s="7" t="inlineStr">
@@ -1565,7 +1565,7 @@
       <c r="L6" s="9" t="inlineStr"/>
       <c r="M6" s="9" t="inlineStr">
         <is>
-          <t>冷酒 / ぬる燗 / 燗酒</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="N6" s="9" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O6" s="9" t="inlineStr">
         <is>
-          <t>限定流通</t>
+          <t>一般流通</t>
         </is>
       </c>
       <c r="P6" s="9" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q6" s="9" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="R6" s="9" t="inlineStr">
         <is>
-          <t>https://shop.kamotsuru.jp/SHOP/GP-A1.html</t>
+          <t>https://shop.kamotsuru.jp/SHOP/itteki720.html</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="P7" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q7" s="7" t="inlineStr">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="P8" s="9" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q8" s="9" t="inlineStr">
@@ -1832,7 +1832,7 @@
       </c>
       <c r="P9" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q9" s="7" t="inlineStr">
@@ -1916,7 +1916,7 @@
       </c>
       <c r="P10" s="9" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q10" s="9" t="inlineStr">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="P11" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q11" s="7" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="P12" s="9" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q12" s="9" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="P13" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q13" s="7" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="P14" s="9" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q14" s="9" t="inlineStr">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="P15" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q15" s="7" t="inlineStr">
@@ -2448,7 +2448,7 @@
       </c>
       <c r="P16" s="9" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q16" s="9" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="P17" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q17" s="7" t="inlineStr">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="P18" s="9" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q18" s="9" t="inlineStr">
@@ -2704,7 +2704,7 @@
       </c>
       <c r="P19" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q19" s="7" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="P20" s="9" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q20" s="9" t="inlineStr">
@@ -2872,7 +2872,7 @@
       </c>
       <c r="P21" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q21" s="7" t="inlineStr">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="P22" s="9" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q22" s="9" t="inlineStr">
@@ -3040,7 +3040,7 @@
       </c>
       <c r="P23" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q23" s="7" t="inlineStr">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="P24" s="9" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q24" s="9" t="inlineStr">
@@ -3212,7 +3212,7 @@
       </c>
       <c r="P25" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q25" s="7" t="inlineStr">
@@ -3300,7 +3300,7 @@
       </c>
       <c r="P26" s="9" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q26" s="9" t="inlineStr">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="P27" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q27" s="7" t="inlineStr">
@@ -3468,7 +3468,7 @@
       </c>
       <c r="P28" s="9" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q28" s="9" t="inlineStr">
@@ -3552,7 +3552,7 @@
       </c>
       <c r="P29" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q29" s="7" t="inlineStr">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="P30" s="9" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q30" s="9" t="inlineStr">
@@ -3728,7 +3728,7 @@
       </c>
       <c r="P31" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q31" s="7" t="inlineStr">
@@ -3816,7 +3816,7 @@
       </c>
       <c r="P32" s="9" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q32" s="9" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="P33" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q33" s="7" t="inlineStr">
@@ -3992,7 +3992,7 @@
       </c>
       <c r="P34" s="9" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q34" s="9" t="inlineStr">
@@ -4080,7 +4080,7 @@
       </c>
       <c r="P35" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q35" s="7" t="inlineStr">
@@ -4164,7 +4164,7 @@
       </c>
       <c r="P36" s="9" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q36" s="9" t="inlineStr">
@@ -4248,7 +4248,7 @@
       </c>
       <c r="P37" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q37" s="7" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="P38" s="9" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q38" s="9" t="inlineStr">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="P39" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q39" s="7" t="inlineStr">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="P40" s="9" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q40" s="9" t="inlineStr">
@@ -4588,7 +4588,7 @@
       </c>
       <c r="P41" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q41" s="7" t="inlineStr">
@@ -4672,7 +4672,7 @@
       </c>
       <c r="P42" s="9" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q42" s="9" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="P43" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q43" s="7" t="inlineStr">
@@ -4840,7 +4840,7 @@
       </c>
       <c r="P44" s="9" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q44" s="9" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="P45" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q45" s="7" t="inlineStr">
@@ -5012,7 +5012,7 @@
       </c>
       <c r="P46" s="9" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q46" s="9" t="inlineStr">
@@ -5100,7 +5100,7 @@
       </c>
       <c r="P47" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q47" s="7" t="inlineStr">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="P48" s="9" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q48" s="9" t="inlineStr">
@@ -5260,7 +5260,7 @@
       </c>
       <c r="P49" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q49" s="7" t="inlineStr">
@@ -5340,7 +5340,7 @@
       </c>
       <c r="P50" s="9" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="Q50" s="9" t="inlineStr">
@@ -5354,8 +5354,512 @@
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>西条エリア7蔵</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>賀茂鶴酒造</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>賀茂鶴</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr"/>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>賀茂鶴 光壽</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G51" s="7" t="inlineStr">
+        <is>
+          <t>公式直営ECで現行販売するプレミアム・スパークリングの主要ライン</t>
+        </is>
+      </c>
+      <c r="H51" s="7" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I51" s="7" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J51" s="7" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K51" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="L51" s="7" t="inlineStr"/>
+      <c r="M51" s="7" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N51" s="7" t="inlineStr">
+        <is>
+          <t>750ml</t>
+        </is>
+      </c>
+      <c r="O51" s="7" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="P51" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Q51" s="7" t="inlineStr">
+        <is>
+          <t>https://shop.kamotsuru.jp/SHOP/kouju750.html</t>
+        </is>
+      </c>
+      <c r="R51" s="7" t="inlineStr">
+        <is>
+          <t>https://shop.kamotsuru.jp/SHOP/kouju750.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="9" t="inlineStr">
+        <is>
+          <t>西条エリア7蔵</t>
+        </is>
+      </c>
+      <c r="B52" s="9" t="inlineStr">
+        <is>
+          <t>賀茂鶴酒造</t>
+        </is>
+      </c>
+      <c r="C52" s="9" t="inlineStr">
+        <is>
+          <t>賀茂鶴</t>
+        </is>
+      </c>
+      <c r="D52" s="9" t="inlineStr"/>
+      <c r="E52" s="9" t="inlineStr">
+        <is>
+          <t>純米大吟醸 瑞兆賀茂鶴</t>
+        </is>
+      </c>
+      <c r="F52" s="9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G52" s="9" t="inlineStr">
+        <is>
+          <t>公式直営ECで現行販売する高級純米大吟醸</t>
+        </is>
+      </c>
+      <c r="H52" s="9" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I52" s="9" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J52" s="9" t="inlineStr">
+        <is>
+          <t>純米大吟醸</t>
+        </is>
+      </c>
+      <c r="K52" s="9" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="L52" s="9" t="inlineStr"/>
+      <c r="M52" s="9" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N52" s="9" t="inlineStr">
+        <is>
+          <t>720ml</t>
+        </is>
+      </c>
+      <c r="O52" s="9" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="P52" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Q52" s="9" t="inlineStr">
+        <is>
+          <t>https://shop.kamotsuru.jp/SHOP/zuicho720.html</t>
+        </is>
+      </c>
+      <c r="R52" s="9" t="inlineStr">
+        <is>
+          <t>https://shop.kamotsuru.jp/SHOP/zuicho720.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>西条エリア7蔵</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>賀茂鶴酒造</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>賀茂鶴</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr"/>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>大吟醸 吉祥 賀茂鶴</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G53" s="7" t="inlineStr">
+        <is>
+          <t>公式直営ECで現行販売する高級大吟醸</t>
+        </is>
+      </c>
+      <c r="H53" s="7" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I53" s="7" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J53" s="7" t="inlineStr">
+        <is>
+          <t>大吟醸</t>
+        </is>
+      </c>
+      <c r="K53" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="L53" s="7" t="inlineStr"/>
+      <c r="M53" s="7" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N53" s="7" t="inlineStr">
+        <is>
+          <t>720ml</t>
+        </is>
+      </c>
+      <c r="O53" s="7" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="P53" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Q53" s="7" t="inlineStr">
+        <is>
+          <t>https://shop.kamotsuru.jp/SHOP/kissho720.html</t>
+        </is>
+      </c>
+      <c r="R53" s="7" t="inlineStr">
+        <is>
+          <t>https://shop.kamotsuru.jp/SHOP/kissho720.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>西条エリア7蔵</t>
+        </is>
+      </c>
+      <c r="B54" s="9" t="inlineStr">
+        <is>
+          <t>賀茂鶴酒造</t>
+        </is>
+      </c>
+      <c r="C54" s="9" t="inlineStr">
+        <is>
+          <t>賀茂鶴</t>
+        </is>
+      </c>
+      <c r="D54" s="9" t="inlineStr"/>
+      <c r="E54" s="9" t="inlineStr">
+        <is>
+          <t>大吟醸 天凜</t>
+        </is>
+      </c>
+      <c r="F54" s="9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G54" s="9" t="inlineStr">
+        <is>
+          <t>公式直営ECで現行販売する高級大吟醸</t>
+        </is>
+      </c>
+      <c r="H54" s="9" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I54" s="9" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J54" s="9" t="inlineStr">
+        <is>
+          <t>大吟醸</t>
+        </is>
+      </c>
+      <c r="K54" s="9" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="L54" s="9" t="inlineStr"/>
+      <c r="M54" s="9" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N54" s="9" t="inlineStr">
+        <is>
+          <t>720ml</t>
+        </is>
+      </c>
+      <c r="O54" s="9" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="P54" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Q54" s="9" t="inlineStr">
+        <is>
+          <t>https://shop.kamotsuru.jp/SHOP/tenrin720.html</t>
+        </is>
+      </c>
+      <c r="R54" s="9" t="inlineStr">
+        <is>
+          <t>https://shop.kamotsuru.jp/SHOP/tenrin720.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>西条エリア7蔵</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>賀茂鶴酒造</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>賀茂鶴</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr"/>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>大吟醸 吟凛雅</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G55" s="7" t="inlineStr">
+        <is>
+          <t>公式直営ECで現行販売するプレミアム大吟醸</t>
+        </is>
+      </c>
+      <c r="H55" s="7" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I55" s="7" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J55" s="7" t="inlineStr">
+        <is>
+          <t>大吟醸</t>
+        </is>
+      </c>
+      <c r="K55" s="7" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="L55" s="7" t="inlineStr"/>
+      <c r="M55" s="7" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N55" s="7" t="inlineStr">
+        <is>
+          <t>900ml</t>
+        </is>
+      </c>
+      <c r="O55" s="7" t="inlineStr">
+        <is>
+          <t>一般流通</t>
+        </is>
+      </c>
+      <c r="P55" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Q55" s="7" t="inlineStr">
+        <is>
+          <t>https://shop.kamotsuru.jp/SHOP/ginringa900.html</t>
+        </is>
+      </c>
+      <c r="R55" s="7" t="inlineStr">
+        <is>
+          <t>https://shop.kamotsuru.jp/SHOP/ginringa900.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="9" t="inlineStr">
+        <is>
+          <t>西条エリア7蔵</t>
+        </is>
+      </c>
+      <c r="B56" s="9" t="inlineStr">
+        <is>
+          <t>賀茂鶴酒造</t>
+        </is>
+      </c>
+      <c r="C56" s="9" t="inlineStr">
+        <is>
+          <t>酒中在心</t>
+        </is>
+      </c>
+      <c r="D56" s="9" t="inlineStr"/>
+      <c r="E56" s="9" t="inlineStr">
+        <is>
+          <t>酒中在心 鶯 純米大吟醸 山田錦</t>
+        </is>
+      </c>
+      <c r="F56" s="9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G56" s="9" t="inlineStr">
+        <is>
+          <t>酒中在心シリーズの現行純米大吟醸</t>
+        </is>
+      </c>
+      <c r="H56" s="9" t="inlineStr">
+        <is>
+          <t>収録済</t>
+        </is>
+      </c>
+      <c r="I56" s="9" t="inlineStr">
+        <is>
+          <t>SKU確認済</t>
+        </is>
+      </c>
+      <c r="J56" s="9" t="inlineStr">
+        <is>
+          <t>純米大吟醸</t>
+        </is>
+      </c>
+      <c r="K56" s="9" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="L56" s="9" t="inlineStr"/>
+      <c r="M56" s="9" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="N56" s="9" t="inlineStr">
+        <is>
+          <t>720ml</t>
+        </is>
+      </c>
+      <c r="O56" s="9" t="inlineStr">
+        <is>
+          <t>限定流通</t>
+        </is>
+      </c>
+      <c r="P56" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Q56" s="9" t="inlineStr">
+        <is>
+          <t>https://shop.kamotsuru.jp/SHOP/shutyuzaishin-uguisu_720.html</t>
+        </is>
+      </c>
+      <c r="R56" s="9" t="inlineStr">
+        <is>
+          <t>https://shop.kamotsuru.jp/SHOP/shutyuzaishin-uguisu_720.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:R50"/>
+  <autoFilter ref="A4:R56"/>
   <mergeCells count="2">
     <mergeCell ref="A2:R2"/>
     <mergeCell ref="A1:R1"/>
@@ -5561,7 +6065,7 @@
       <c r="G6" s="9" t="inlineStr"/>
       <c r="H6" s="9" t="inlineStr">
         <is>
-          <t>冷酒 / ぬる燗 / 燗酒</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="I6" s="9" t="inlineStr">
@@ -5571,7 +6075,7 @@
       </c>
       <c r="J6" s="9" t="inlineStr">
         <is>
-          <t>限定流通</t>
+          <t>一般流通</t>
         </is>
       </c>
       <c r="K6" s="9" t="inlineStr">
@@ -5586,7 +6090,7 @@
       </c>
       <c r="M6" s="8" t="inlineStr">
         <is>
-          <t>https://shop.kamotsuru.jp/SHOP/GP-A1.html</t>
+          <t>https://shop.kamotsuru.jp/SHOP/itteki720.html</t>
         </is>
       </c>
     </row>
